--- a/mlb_weather_professional_v5_2026_10_03.xlsx
+++ b/mlb_weather_professional_v5_2026_10_03.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="370">
   <si>
     <t>Date</t>
   </si>
@@ -407,15 +407,12 @@
     <t>PROJECTED: TEMPERATURE</t>
   </si>
   <si>
+    <t>Mostly clear</t>
+  </si>
+  <si>
     <t>Clear</t>
   </si>
   <si>
-    <t>Partly cloudy</t>
-  </si>
-  <si>
-    <t>Light drizzle</t>
-  </si>
-  <si>
     <t>Overcast</t>
   </si>
   <si>
@@ -425,7 +422,7 @@
     <t>GOOD DATA</t>
   </si>
   <si>
-    <t>🟡 6.1 mph Cross (RF → LF)</t>
+    <t>🟡 7.0 mph Cross (RF → LF)</t>
   </si>
   <si>
     <t>⚪ Light Variable</t>
@@ -440,9 +437,6 @@
     <t>S</t>
   </si>
   <si>
-    <t>NNW</t>
-  </si>
-  <si>
     <t>FORECAST MODEL</t>
   </si>
   <si>
@@ -455,16 +449,16 @@
     <t>B</t>
   </si>
   <si>
-    <t>Density 57 | Wind 37 | Temp 42 | Altitude 55 | Confidence 93%</t>
-  </si>
-  <si>
-    <t>Density 87 | Wind 59 | Temp 82 | Altitude 75 | Confidence 87%</t>
-  </si>
-  <si>
-    <t>Density 61 | Wind 50 | Temp 59 | Altitude 56 | Confidence 85%</t>
-  </si>
-  <si>
-    <t>Density 61 | Wind 50 | Temp 33 | Altitude 57 | Confidence 94%</t>
+    <t>Density 58 | Wind 36 | Temp 43 | Altitude 55 | Confidence 94%</t>
+  </si>
+  <si>
+    <t>Density 88 | Wind 59 | Temp 83 | Altitude 76 | Confidence 91%</t>
+  </si>
+  <si>
+    <t>Density 61 | Wind 50 | Temp 60 | Altitude 56 | Confidence 83%</t>
+  </si>
+  <si>
+    <t>Density 61 | Wind 50 | Temp 33 | Altitude 57 | Confidence 96%</t>
   </si>
   <si>
     <t>🟧 Below Average</t>
@@ -482,13 +476,13 @@
     <t>SHIFTING</t>
   </si>
   <si>
-    <t>1st-3rd: CROSS RF → LF -2.9 mph | 4th-5th: CROSS RF → LF -4.1 mph | 6th-7th: IN FROM RF -5.9 mph | 8th-9th: IN FROM RF -5.5 mph</t>
-  </si>
-  <si>
-    <t>1st-3rd: OUT TO LCF +2.4 mph | 4th-5th: OUT TO CF +3.7 mph | 6th-7th: OUT TO RCF +3.8 mph | 8th-9th: OUT TO RCF +5.7 mph</t>
-  </si>
-  <si>
-    <t>1st-3rd: LIGHT / VARIABLE +0.0 mph | 4th-5th: IN FROM RF +0.0 mph | 6th-7th: IN FROM RF +0.0 mph | 8th-9th: CROSS RF → LF +0.0 mph</t>
+    <t>1st-3rd: CROSS RF → LF -3.2 mph | 4th-5th: IN FROM RF -5.0 mph | 6th-7th: IN FROM RF -5.8 mph | 8th-9th: IN FROM RF -5.3 mph</t>
+  </si>
+  <si>
+    <t>1st-3rd: OUT TO LCF +2.5 mph | 4th-5th: OUT TO RCF +3.7 mph | 6th-7th: OUT TO RCF +3.6 mph | 8th-9th: OUT TO RCF +6.2 mph</t>
+  </si>
+  <si>
+    <t>1st-3rd: OUT TO LF +0.0 mph | 4th-5th: LIGHT / VARIABLE +0.0 mph | 6th-7th: VARIABLE / CROSSWIND +0.0 mph | 8th-9th: IN FROM RF +0.0 mph</t>
   </si>
   <si>
     <t>1st-3rd: CROSS RF → LF +0.0 mph | 4th-5th: CROSS RF → LF +0.0 mph | 6th-7th: CROSS RF → LF +0.0 mph | 8th-9th: CROSS RF → LF +0.0 mph</t>
@@ -497,7 +491,25 @@
     <t>MODEL_VERTICAL_PROFILE</t>
   </si>
   <si>
-    <t>FIRST RUN</t>
+    <t>WORSENING RAPIDLY</t>
+  </si>
+  <si>
+    <t>IMPROVING RAPIDLY</t>
+  </si>
+  <si>
+    <t>IMPROVING</t>
+  </si>
+  <si>
+    <t>2026-10-03 02:57:41 UTC</t>
+  </si>
+  <si>
+    <t>2026-10-03 02:57:52 UTC</t>
+  </si>
+  <si>
+    <t>2026-10-03 02:58:04 UTC</t>
+  </si>
+  <si>
+    <t>2026-10-03 02:58:05 UTC</t>
   </si>
   <si>
     <t>LOW</t>
@@ -506,19 +518,16 @@
     <t>NONE (ROOF)</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>2026-10-02 07:57:41 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-10-02 07:57:52 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-10-02 07:58:04 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-10-02 07:58:05 PM PDT</t>
+    <t>2026-10-03 01:11:28 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-10-03 01:11:38 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-10-03 01:11:48 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-10-03 01:11:49 PM PDT</t>
   </si>
   <si>
     <t>Period</t>
@@ -1016,36 +1025,33 @@
     <t>10:30 PM CDT</t>
   </si>
   <si>
-    <t>2026-10-03 02:57:41 UTC</t>
-  </si>
-  <si>
-    <t>2026-10-03 02:57:52 UTC</t>
-  </si>
-  <si>
-    <t>2026-10-03 02:58:04 UTC</t>
-  </si>
-  <si>
-    <t>2026-10-03 02:58:05 UTC</t>
-  </si>
-  <si>
-    <t>2026-10-02T19:46:31+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-02T22:31:34+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-02T20:12:08+00:00</t>
-  </si>
-  <si>
-    <t>2026-10-03T01:51:59+00:00</t>
+    <t>2026-10-03 20:11:28 UTC</t>
+  </si>
+  <si>
+    <t>2026-10-03 20:11:38 UTC</t>
+  </si>
+  <si>
+    <t>2026-10-03 20:11:48 UTC</t>
+  </si>
+  <si>
+    <t>2026-10-03 20:11:49 UTC</t>
+  </si>
+  <si>
+    <t>2026-10-03T19:47:05+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-03T19:21:37+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-03T18:57:17+00:00</t>
+  </si>
+  <si>
+    <t>2026-10-03T19:36:32+00:00</t>
   </si>
   <si>
     <t>NWS 28.2%; GFS_HRRR 41.1%; ECMWF 16.5%; ICON 14.1%</t>
   </si>
   <si>
-    <t>NWS 30.0%; GFS_HRRR 35.0%; ECMWF 20.0%; ICON 15.0%</t>
-  </si>
-  <si>
     <t>YES</t>
   </si>
   <si>
@@ -1082,27 +1088,18 @@
     <t>2026-10-03T23:00</t>
   </si>
   <si>
-    <t>Heavy drizzle</t>
-  </si>
-  <si>
     <t>CONSENSUS_DIRECTION_HELD_CONSTANT</t>
   </si>
   <si>
     <t>SW</t>
   </si>
   <si>
-    <t>WSW</t>
+    <t>SSE</t>
   </si>
   <si>
     <t>ENE</t>
   </si>
   <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>ESE</t>
-  </si>
-  <si>
     <t>SSW</t>
   </si>
   <si>
@@ -1115,13 +1112,16 @@
     <t>OUT TO LCF</t>
   </si>
   <si>
-    <t>OUT TO CF</t>
-  </si>
-  <si>
     <t>OUT TO RCF</t>
   </si>
   <si>
+    <t>OUT TO LF</t>
+  </si>
+  <si>
     <t>LIGHT / VARIABLE</t>
+  </si>
+  <si>
+    <t>VARIABLE / CROSSWIND</t>
   </si>
   <si>
     <t>NEUTRAL</t>
@@ -1638,7 +1638,7 @@
     <col min="65" max="69" width="34.7109375" customWidth="1"/>
     <col min="70" max="70" width="31.7109375" customWidth="1"/>
     <col min="71" max="71" width="34.7109375" customWidth="1"/>
-    <col min="72" max="72" width="16.7109375" customWidth="1"/>
+    <col min="72" max="72" width="19.7109375" customWidth="1"/>
     <col min="73" max="73" width="34.7109375" customWidth="1"/>
     <col min="74" max="74" width="30.7109375" customWidth="1"/>
     <col min="75" max="77" width="34.7109375" customWidth="1"/>
@@ -1988,58 +1988,58 @@
         <v>128</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="s">
+        <v>131</v>
+      </c>
+      <c r="N2" t="s">
         <v>132</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="R2">
+        <v>58.5</v>
+      </c>
+      <c r="S2" t="s">
         <v>133</v>
       </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>63.8</v>
-      </c>
-      <c r="R2">
-        <v>54.1</v>
-      </c>
-      <c r="S2" t="s">
-        <v>134</v>
-      </c>
       <c r="T2">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="U2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="V2">
         <v>-0.3</v>
       </c>
       <c r="W2">
-        <v>-4.5</v>
+        <v>-5</v>
       </c>
       <c r="X2">
-        <v>-6.8</v>
+        <v>-7.7</v>
       </c>
       <c r="Y2">
-        <v>-6.1</v>
+        <v>-7</v>
       </c>
       <c r="AA2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AB2">
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>46.6</v>
+        <v>46.3</v>
       </c>
       <c r="AD2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AE2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AF2">
         <v>-2</v>
@@ -2048,16 +2048,16 @@
         <v>-2</v>
       </c>
       <c r="AH2">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="AI2">
-        <v>92.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AJ2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AK2">
-        <v>-4.2</v>
+        <v>-4.5</v>
       </c>
       <c r="AL2">
         <v>-4</v>
@@ -2075,127 +2075,139 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>43.9</v>
+        <v>53.7</v>
       </c>
       <c r="AR2">
-        <v>87.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="AS2">
-        <v>97.09999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="AT2">
-        <v>-6.7</v>
+        <v>-7.1</v>
       </c>
       <c r="AU2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AV2">
         <v>25.2</v>
       </c>
       <c r="AW2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AX2">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="AY2">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="AZ2">
-        <v>1.2004</v>
+        <v>1.1987</v>
       </c>
       <c r="BA2">
-        <v>560</v>
+        <v>594</v>
       </c>
       <c r="BB2">
-        <v>1007.5</v>
+        <v>1007.3</v>
       </c>
       <c r="BC2">
-        <v>46.2</v>
+        <v>49</v>
       </c>
       <c r="BD2">
-        <v>64.5</v>
+        <v>65</v>
       </c>
       <c r="BE2">
-        <v>53.1</v>
+        <v>57.4</v>
       </c>
       <c r="BF2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BG2">
         <v>0.134</v>
       </c>
       <c r="BH2">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="BI2">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BJ2">
-        <v>9.4</v>
+        <v>10.1</v>
       </c>
       <c r="BK2">
-        <v>10.3</v>
+        <v>11.1</v>
       </c>
       <c r="BL2">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="BM2">
-        <v>-3.2</v>
+        <v>-3.5</v>
       </c>
       <c r="BN2">
-        <v>-4.1</v>
+        <v>-4.5</v>
       </c>
       <c r="BO2">
-        <v>-4.6</v>
+        <v>-5.1</v>
       </c>
       <c r="BP2">
-        <v>-5.3</v>
+        <v>-5.7</v>
       </c>
       <c r="BQ2">
+        <v>-6.1</v>
+      </c>
+      <c r="BR2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BS2">
+        <v>-4.5</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>156</v>
+      </c>
+      <c r="BU2">
+        <v>-7.6</v>
+      </c>
+      <c r="BV2">
+        <v>0.5</v>
+      </c>
+      <c r="BW2">
+        <v>-0.4</v>
+      </c>
+      <c r="BX2">
+        <v>0</v>
+      </c>
+      <c r="BY2">
+        <v>0</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>159</v>
+      </c>
+      <c r="CA2">
+        <v>-7.6</v>
+      </c>
+      <c r="CB2">
+        <v>-0.4</v>
+      </c>
+      <c r="CC2">
+        <v>0.5</v>
+      </c>
+      <c r="CD2">
+        <v>0</v>
+      </c>
+      <c r="CE2">
         <v>-5.6</v>
       </c>
-      <c r="BR2">
-        <v>8.5</v>
-      </c>
-      <c r="BS2">
-        <v>-4.2</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>158</v>
-      </c>
-      <c r="BU2">
-        <v>0</v>
-      </c>
-      <c r="BV2">
-        <v>0</v>
-      </c>
-      <c r="BW2">
-        <v>0</v>
-      </c>
-      <c r="BX2">
-        <v>0</v>
-      </c>
-      <c r="BY2">
-        <v>0</v>
-      </c>
-      <c r="CA2">
-        <v>0</v>
-      </c>
-      <c r="CB2">
-        <v>0</v>
-      </c>
-      <c r="CC2">
-        <v>0</v>
-      </c>
-      <c r="CD2">
+      <c r="CF2">
+        <v>64.5</v>
+      </c>
+      <c r="CG2">
         <v>0</v>
       </c>
       <c r="CH2">
-        <v>-5.6</v>
+        <v>-6</v>
       </c>
       <c r="CI2">
-        <v>64.5</v>
+        <v>65</v>
       </c>
       <c r="CJ2">
         <v>0</v>
@@ -2207,22 +2219,22 @@
         <v>34</v>
       </c>
       <c r="CM2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CN2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="CO2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CP2">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CQ2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="CR2">
-        <v>431.2</v>
+        <v>24.4</v>
       </c>
       <c r="CS2">
         <v>5</v>
@@ -2263,73 +2275,73 @@
         <v>129</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="s">
+        <v>131</v>
+      </c>
+      <c r="N3" t="s">
         <v>132</v>
       </c>
-      <c r="N3" t="s">
-        <v>133</v>
-      </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>101.2</v>
+        <v>102.6</v>
       </c>
       <c r="R3">
-        <v>17.2</v>
+        <v>18</v>
       </c>
       <c r="S3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T3">
         <v>2.9</v>
       </c>
       <c r="U3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="V3">
         <v>3.1</v>
       </c>
       <c r="W3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="X3">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Y3">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="AA3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>65.5</v>
+      </c>
+      <c r="AD3" t="s">
         <v>140</v>
       </c>
-      <c r="AB3">
-        <v>0.8</v>
-      </c>
-      <c r="AC3">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>142</v>
-      </c>
       <c r="AE3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AF3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG3">
         <v>7</v>
       </c>
       <c r="AH3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AI3">
-        <v>86.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AJ3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AK3">
         <v>3.5</v>
@@ -2344,58 +2356,58 @@
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>49.1</v>
+        <v>51.2</v>
       </c>
       <c r="AP3">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="AQ3">
         <v>0</v>
       </c>
       <c r="AR3">
-        <v>83.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="AS3">
-        <v>97.5</v>
+        <v>97.3</v>
       </c>
       <c r="AT3">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="AU3" t="s">
+        <v>149</v>
+      </c>
+      <c r="AV3">
+        <v>28.4</v>
+      </c>
+      <c r="AW3" t="s">
         <v>152</v>
       </c>
-      <c r="AV3">
-        <v>28.6</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>154</v>
-      </c>
       <c r="AX3">
-        <v>10.1</v>
+        <v>9.1</v>
       </c>
       <c r="AY3">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AZ3">
-        <v>1.1019</v>
+        <v>1.0988</v>
       </c>
       <c r="BA3">
-        <v>3585</v>
+        <v>3672</v>
       </c>
       <c r="BB3">
-        <v>991.7</v>
+        <v>990.7</v>
       </c>
       <c r="BC3">
-        <v>48.1</v>
+        <v>50.6</v>
       </c>
       <c r="BD3">
-        <v>102.2</v>
+        <v>103</v>
       </c>
       <c r="BE3">
-        <v>17.4</v>
+        <v>18.5</v>
       </c>
       <c r="BF3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BG3">
         <v>0.141</v>
@@ -2413,19 +2425,19 @@
         <v>5.9</v>
       </c>
       <c r="BL3">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="BM3">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="BN3">
         <v>3.5</v>
       </c>
       <c r="BO3">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BP3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BQ3">
         <v>4.9</v>
@@ -2437,43 +2449,55 @@
         <v>3.5</v>
       </c>
       <c r="BT3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="BU3">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BV3">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="BW3">
         <v>0</v>
       </c>
       <c r="BX3">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="BY3">
         <v>0</v>
       </c>
+      <c r="BZ3" t="s">
+        <v>160</v>
+      </c>
       <c r="CA3">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="CB3">
         <v>0</v>
       </c>
       <c r="CC3">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="CD3">
-        <v>0</v>
+        <v>-0.8</v>
+      </c>
+      <c r="CE3">
+        <v>4</v>
+      </c>
+      <c r="CF3">
+        <v>102.2</v>
+      </c>
+      <c r="CG3">
+        <v>0.8</v>
       </c>
       <c r="CH3">
         <v>4</v>
       </c>
       <c r="CI3">
-        <v>102.2</v>
+        <v>103</v>
       </c>
       <c r="CJ3">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="CK3">
         <v>-0.37</v>
@@ -2482,22 +2506,22 @@
         <v>34</v>
       </c>
       <c r="CM3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CN3">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="CO3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="CP3">
-        <v>19.9</v>
+        <v>17.9</v>
       </c>
       <c r="CQ3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CR3">
-        <v>266.3</v>
+        <v>50</v>
       </c>
       <c r="CS3">
         <v>5</v>
@@ -2538,31 +2562,31 @@
         <v>130</v>
       </c>
       <c r="L4">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="M4" t="s">
+        <v>131</v>
+      </c>
+      <c r="N4" t="s">
         <v>132</v>
       </c>
-      <c r="N4" t="s">
-        <v>133</v>
-      </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>81.7</v>
+        <v>84.2</v>
       </c>
       <c r="R4">
-        <v>81.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="S4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="T4">
         <v>0</v>
       </c>
       <c r="U4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="V4">
         <v>0</v>
@@ -2577,19 +2601,19 @@
         <v>0</v>
       </c>
       <c r="AA4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AB4">
-        <v>41.6</v>
+        <v>37.2</v>
       </c>
       <c r="AC4">
         <v>50</v>
       </c>
       <c r="AD4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AE4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AF4">
         <v>0</v>
@@ -2601,10 +2625,10 @@
         <v>0</v>
       </c>
       <c r="AI4">
-        <v>85.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AJ4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AK4">
         <v>0</v>
@@ -2628,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="AR4">
-        <v>56.3</v>
+        <v>38.9</v>
       </c>
       <c r="AS4">
         <v>100</v>
@@ -2637,16 +2661,16 @@
         <v>0</v>
       </c>
       <c r="AU4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AV4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AX4">
-        <v>48.3</v>
+        <v>73.5</v>
       </c>
       <c r="AY4">
         <v>0</v>
@@ -2658,19 +2682,19 @@
         <v>858</v>
       </c>
       <c r="BB4">
-        <v>1014.5</v>
+        <v>1014.8</v>
       </c>
       <c r="BC4">
-        <v>75.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="BD4">
-        <v>80.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="BE4">
-        <v>85.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="BF4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BG4">
         <v>0.187</v>
@@ -2715,40 +2739,52 @@
         <v>158</v>
       </c>
       <c r="BU4">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BV4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BW4">
         <v>0</v>
       </c>
       <c r="BX4">
-        <v>0</v>
+        <v>-4.4</v>
       </c>
       <c r="BY4">
         <v>0</v>
       </c>
+      <c r="BZ4" t="s">
+        <v>161</v>
+      </c>
       <c r="CA4">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="CB4">
         <v>0</v>
       </c>
       <c r="CC4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="CD4">
-        <v>0</v>
+        <v>-4.4</v>
+      </c>
+      <c r="CE4">
+        <v>0</v>
+      </c>
+      <c r="CF4">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="CG4">
+        <v>41.6</v>
       </c>
       <c r="CH4">
         <v>0</v>
       </c>
       <c r="CI4">
-        <v>80.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="CJ4">
-        <v>41.6</v>
+        <v>37.2</v>
       </c>
       <c r="CK4">
         <v>0.09</v>
@@ -2757,22 +2793,22 @@
         <v>35</v>
       </c>
       <c r="CM4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="CN4">
         <v>0</v>
       </c>
       <c r="CO4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CP4">
-        <v>16.9</v>
+        <v>17.8</v>
       </c>
       <c r="CQ4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="CR4">
-        <v>405.9</v>
+        <v>74.5</v>
       </c>
       <c r="CS4">
         <v>5</v>
@@ -2810,16 +2846,16 @@
         <v>127</v>
       </c>
       <c r="K5" t="s">
+        <v>129</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
         <v>131</v>
       </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>132</v>
-      </c>
-      <c r="N5" t="s">
-        <v>133</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -2828,43 +2864,43 @@
         <v>56.5</v>
       </c>
       <c r="R5">
-        <v>80.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="S5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="T5">
         <v>0</v>
       </c>
       <c r="U5" t="s">
+        <v>137</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="s">
         <v>138</v>
       </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>140</v>
-      </c>
       <c r="AB5">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AC5">
         <v>49.9</v>
       </c>
       <c r="AD5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AE5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -2876,10 +2912,10 @@
         <v>-0</v>
       </c>
       <c r="AI5">
-        <v>94.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="AJ5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -2903,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="AR5">
-        <v>91.5</v>
+        <v>95.7</v>
       </c>
       <c r="AS5">
         <v>100</v>
@@ -2912,19 +2948,19 @@
         <v>0</v>
       </c>
       <c r="AU5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AV5">
         <v>15</v>
       </c>
       <c r="AW5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AX5">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="AY5">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="AZ5">
         <v>1.1896</v>
@@ -2933,19 +2969,19 @@
         <v>858</v>
       </c>
       <c r="BB5">
-        <v>996.5</v>
+        <v>995.7</v>
       </c>
       <c r="BC5">
-        <v>51.1</v>
+        <v>51.3</v>
       </c>
       <c r="BD5">
-        <v>55.6</v>
+        <v>55.9</v>
       </c>
       <c r="BE5">
-        <v>84.5</v>
+        <v>84.7</v>
       </c>
       <c r="BF5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BG5">
         <v>0.143</v>
@@ -2990,40 +3026,52 @@
         <v>158</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="BW5">
         <v>0</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="BY5">
         <v>0</v>
       </c>
+      <c r="BZ5" t="s">
+        <v>162</v>
+      </c>
       <c r="CA5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="CB5">
         <v>0</v>
       </c>
       <c r="CC5">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="CD5">
-        <v>0</v>
+        <v>-0.6</v>
+      </c>
+      <c r="CE5">
+        <v>0</v>
+      </c>
+      <c r="CF5">
+        <v>55.6</v>
+      </c>
+      <c r="CG5">
+        <v>1.2</v>
       </c>
       <c r="CH5">
         <v>0</v>
       </c>
       <c r="CI5">
-        <v>55.6</v>
+        <v>55.9</v>
       </c>
       <c r="CJ5">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="CK5">
         <v>-0.24</v>
@@ -3032,22 +3080,22 @@
         <v>34</v>
       </c>
       <c r="CM5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="CN5">
         <v>0</v>
       </c>
       <c r="CO5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="CP5">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="CQ5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="CR5">
-        <v>66.09999999999999</v>
+        <v>35.3</v>
       </c>
       <c r="CS5">
         <v>5</v>
@@ -3132,7 +3180,7 @@
     <col min="50" max="50" width="25.7109375" customWidth="1"/>
     <col min="51" max="51" width="18.7109375" customWidth="1"/>
     <col min="52" max="52" width="28.7109375" customWidth="1"/>
-    <col min="53" max="53" width="15.7109375" customWidth="1"/>
+    <col min="53" max="53" width="14.7109375" customWidth="1"/>
     <col min="54" max="54" width="10.7109375" customWidth="1"/>
     <col min="55" max="55" width="14.7109375" customWidth="1"/>
     <col min="56" max="56" width="13.7109375" customWidth="1"/>
@@ -3164,8 +3212,7 @@
     <col min="105" max="105" width="22.7109375" customWidth="1"/>
     <col min="106" max="106" width="11.7109375" customWidth="1"/>
     <col min="107" max="107" width="19.7109375" customWidth="1"/>
-    <col min="108" max="108" width="21.7109375" customWidth="1"/>
-    <col min="109" max="109" width="22.7109375" customWidth="1"/>
+    <col min="108" max="109" width="22.7109375" customWidth="1"/>
     <col min="110" max="110" width="28.7109375" customWidth="1"/>
     <col min="111" max="111" width="26.7109375" customWidth="1"/>
     <col min="112" max="112" width="25.7109375" customWidth="1"/>
@@ -3216,142 +3263,142 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>94</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>95</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>96</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AY1" s="1" t="s">
         <v>11</v>
@@ -3360,310 +3407,310 @@
         <v>12</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="EY1" s="1" t="s">
         <v>93</v>
@@ -3672,16 +3719,16 @@
         <v>92</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:160">
@@ -3698,43 +3745,43 @@
         <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F2" t="s">
         <v>114</v>
       </c>
       <c r="G2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="H2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J2">
-        <v>431.2</v>
+        <v>24.4</v>
       </c>
       <c r="K2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <v>5</v>
       </c>
       <c r="M2">
-        <v>1.37</v>
+        <v>0.78</v>
       </c>
       <c r="N2">
-        <v>1.08</v>
+        <v>0.66</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>11.9</v>
+        <v>7.4</v>
       </c>
       <c r="Q2">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -3743,22 +3790,22 @@
         <v>100</v>
       </c>
       <c r="T2">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U2">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="V2">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="W2">
-        <v>-5.1</v>
+        <v>-4.9</v>
       </c>
       <c r="X2">
-        <v>-3.4</v>
+        <v>-3.5</v>
       </c>
       <c r="Y2">
-        <v>-1.6</v>
+        <v>-2.1</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -3767,58 +3814,58 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>11.3</v>
+        <v>8.6</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>97.09999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="AE2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AF2">
         <v>-1.2</v>
       </c>
       <c r="AG2">
-        <v>-3</v>
+        <v>-3.2</v>
       </c>
       <c r="AH2">
-        <v>-4.2</v>
+        <v>-4.4</v>
       </c>
       <c r="AI2">
-        <v>-4.8</v>
+        <v>-5</v>
       </c>
       <c r="AJ2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AK2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AM2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AN2">
         <v>1</v>
       </c>
       <c r="AO2">
-        <v>8.699999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="AP2">
-        <v>93.8</v>
+        <v>93.2</v>
       </c>
       <c r="AQ2">
-        <v>43.5</v>
+        <v>43.1</v>
       </c>
       <c r="AR2">
         <v>0.92</v>
       </c>
       <c r="AS2">
-        <v>0.884</v>
+        <v>0.885</v>
       </c>
       <c r="AT2">
         <v>2</v>
@@ -3836,34 +3883,34 @@
         <v>0.3</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA2" t="s">
         <v>128</v>
       </c>
       <c r="BB2">
-        <v>63.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="BC2">
-        <v>62.2</v>
+        <v>60.8</v>
       </c>
       <c r="BD2">
-        <v>46</v>
+        <v>49.3</v>
       </c>
       <c r="BE2">
-        <v>54.1</v>
+        <v>58.5</v>
       </c>
       <c r="BF2">
-        <v>1008.1</v>
+        <v>1008.2</v>
       </c>
       <c r="BG2">
         <v>1026.2</v>
       </c>
       <c r="BH2">
-        <v>26.4</v>
+        <v>41.1</v>
       </c>
       <c r="BI2">
         <v>0</v>
@@ -3872,214 +3919,214 @@
         <v>0</v>
       </c>
       <c r="BK2">
-        <v>83.40000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="BL2">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="BM2">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN2">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="BO2">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="BP2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BQ2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BR2">
         <v>0.132</v>
       </c>
       <c r="BS2">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="BT2">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="BU2">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BV2">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="BX2">
         <v>-0.2</v>
       </c>
       <c r="BY2">
-        <v>-3.5</v>
+        <v>-4</v>
       </c>
       <c r="BZ2">
-        <v>-5.2</v>
+        <v>-5.9</v>
       </c>
       <c r="CA2">
         <v>-0.3</v>
       </c>
       <c r="CB2">
-        <v>-4.5</v>
+        <v>-5</v>
       </c>
       <c r="CC2">
-        <v>-6.7</v>
+        <v>-7.6</v>
       </c>
       <c r="CD2">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="CE2">
-        <v>-5</v>
+        <v>-5.6</v>
       </c>
       <c r="CF2">
-        <v>-7.6</v>
+        <v>-8.6</v>
       </c>
       <c r="CG2">
         <v>-0.4</v>
       </c>
       <c r="CH2">
-        <v>-5.5</v>
+        <v>-6.2</v>
       </c>
       <c r="CI2">
-        <v>-8.5</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="CJ2">
         <v>-0.4</v>
       </c>
       <c r="CK2">
-        <v>-5.9</v>
+        <v>-6.6</v>
       </c>
       <c r="CL2">
-        <v>-9.1</v>
+        <v>-10.3</v>
       </c>
       <c r="CM2">
-        <v>-2.2</v>
+        <v>-2.5</v>
       </c>
       <c r="CN2">
-        <v>-2.9</v>
+        <v>-3.2</v>
       </c>
       <c r="CO2">
+        <v>-3.6</v>
+      </c>
+      <c r="CP2">
+        <v>-4.1</v>
+      </c>
+      <c r="CQ2">
+        <v>-4.3</v>
+      </c>
+      <c r="CR2">
+        <v>9</v>
+      </c>
+      <c r="CS2">
         <v>-3.2</v>
       </c>
-      <c r="CP2">
-        <v>-3.7</v>
-      </c>
-      <c r="CQ2">
-        <v>-3.9</v>
-      </c>
-      <c r="CR2">
-        <v>7.9</v>
-      </c>
-      <c r="CS2">
-        <v>-2.9</v>
-      </c>
       <c r="CT2">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="CU2">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CV2">
-        <v>9.300000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="CW2">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="CX2">
-        <v>12.3</v>
+        <v>11.9</v>
       </c>
       <c r="CY2">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="CZ2">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="DA2">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="DB2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="DC2">
-        <v>51.6</v>
+        <v>52.1</v>
       </c>
       <c r="DD2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="DE2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="DF2">
-        <v>88.2</v>
+        <v>91.7</v>
       </c>
       <c r="DG2">
-        <v>88.2</v>
+        <v>91.7</v>
       </c>
       <c r="DH2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="DI2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="DJ2">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="DK2">
-        <v>-4.4</v>
+        <v>-4.9</v>
       </c>
       <c r="DL2">
         <v>-0.3</v>
       </c>
       <c r="DM2">
-        <v>-6.9</v>
+        <v>-7.8</v>
       </c>
       <c r="DN2">
-        <v>-5.7</v>
+        <v>-6.5</v>
       </c>
       <c r="DO2">
-        <v>-3.9</v>
+        <v>-4.4</v>
       </c>
       <c r="DP2">
         <v>-0.3</v>
       </c>
       <c r="DQ2">
-        <v>-6.1</v>
+        <v>-6.9</v>
       </c>
       <c r="DR2">
-        <v>-4.4</v>
+        <v>-4.9</v>
       </c>
       <c r="DS2">
         <v>-0.3</v>
       </c>
       <c r="DT2">
-        <v>-6.9</v>
+        <v>-7.8</v>
       </c>
       <c r="DU2">
-        <v>-4.5</v>
+        <v>-5</v>
       </c>
       <c r="DV2">
         <v>-0.3</v>
       </c>
       <c r="DW2">
-        <v>-6.8</v>
+        <v>-7.7</v>
       </c>
       <c r="DX2">
-        <v>-6.1</v>
+        <v>-7</v>
       </c>
       <c r="DY2">
-        <v>-2.9</v>
+        <v>-3.2</v>
       </c>
       <c r="DZ2">
-        <v>-2.9</v>
+        <v>-3.2</v>
       </c>
       <c r="EA2">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="EB2">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="EC2">
         <v>0.9</v>
@@ -4094,13 +4141,13 @@
         <v>0.12</v>
       </c>
       <c r="EG2">
-        <v>1.2028</v>
+        <v>1.2005</v>
       </c>
       <c r="EH2" t="s">
         <v>367</v>
       </c>
       <c r="EI2">
-        <v>491</v>
+        <v>540</v>
       </c>
       <c r="EJ2" t="s">
         <v>122</v>
@@ -4109,61 +4156,61 @@
         <v>125</v>
       </c>
       <c r="EL2">
-        <v>43.1</v>
+        <v>42.6</v>
       </c>
       <c r="EM2">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="EN2">
-        <v>-8.699999999999999</v>
+        <v>-9.6</v>
       </c>
       <c r="EO2">
-        <v>-0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="EP2">
         <v>0</v>
       </c>
       <c r="EQ2">
-        <v>0.983</v>
+        <v>0.982</v>
       </c>
       <c r="ER2">
-        <v>39.6</v>
+        <v>38.5</v>
       </c>
       <c r="ES2">
-        <v>45.4</v>
+        <v>45.2</v>
       </c>
       <c r="ET2">
-        <v>51.5</v>
+        <v>51.7</v>
       </c>
       <c r="EU2">
-        <v>46.5</v>
+        <v>46.8</v>
       </c>
       <c r="EV2">
-        <v>68.2</v>
+        <v>69</v>
       </c>
       <c r="EW2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="EX2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="EY2">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="EZ2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="FA2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="FB2">
-        <v>64.09999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="FC2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="FD2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:160">
@@ -4180,43 +4227,43 @@
         <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="H3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J3">
-        <v>431.2</v>
+        <v>24.4</v>
       </c>
       <c r="K3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>5</v>
       </c>
       <c r="M3">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.15</v>
+        <v>0.61</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>11.8</v>
+        <v>7.5</v>
       </c>
       <c r="Q3">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -4225,22 +4272,22 @@
         <v>100</v>
       </c>
       <c r="T3">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="U3">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="V3">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="W3">
-        <v>-6.1</v>
+        <v>-6.7</v>
       </c>
       <c r="X3">
-        <v>-4.7</v>
+        <v>-5.5</v>
       </c>
       <c r="Y3">
-        <v>-2.8</v>
+        <v>-4.2</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -4249,58 +4296,58 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>39.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>97.2</v>
+        <v>97.8</v>
       </c>
       <c r="AE3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AF3">
-        <v>-1.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AG3">
-        <v>-4.1</v>
+        <v>-5</v>
       </c>
       <c r="AH3">
-        <v>-5.7</v>
+        <v>-6.9</v>
       </c>
       <c r="AI3">
-        <v>-6.5</v>
+        <v>-7.8</v>
       </c>
       <c r="AJ3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AK3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AM3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AN3">
         <v>1</v>
       </c>
       <c r="AO3">
-        <v>10.5</v>
+        <v>5.9</v>
       </c>
       <c r="AP3">
-        <v>92.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="AQ3">
-        <v>40.5</v>
+        <v>37.9</v>
       </c>
       <c r="AR3">
         <v>0.92</v>
       </c>
       <c r="AS3">
-        <v>0.868</v>
+        <v>0.861</v>
       </c>
       <c r="AT3">
         <v>2</v>
@@ -4318,25 +4365,25 @@
         <v>0.3</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA3" t="s">
         <v>128</v>
       </c>
       <c r="BB3">
-        <v>64.90000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="BC3">
-        <v>63.4</v>
+        <v>62.9</v>
       </c>
       <c r="BD3">
-        <v>45.7</v>
+        <v>49.8</v>
       </c>
       <c r="BE3">
-        <v>51.2</v>
+        <v>58.6</v>
       </c>
       <c r="BF3">
         <v>1007.6</v>
@@ -4345,7 +4392,7 @@
         <v>1025.6</v>
       </c>
       <c r="BH3">
-        <v>26.3</v>
+        <v>39.8</v>
       </c>
       <c r="BI3">
         <v>0</v>
@@ -4354,139 +4401,139 @@
         <v>0</v>
       </c>
       <c r="BK3">
-        <v>90.5</v>
+        <v>57.3</v>
       </c>
       <c r="BL3">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="BM3">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="BN3">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="BO3">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BP3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BQ3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BR3">
-        <v>0.134</v>
+        <v>0.135</v>
       </c>
       <c r="BS3">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="BT3">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU3">
-        <v>9.1</v>
+        <v>10.1</v>
       </c>
       <c r="BV3">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="BW3">
-        <v>10.6</v>
+        <v>11.7</v>
       </c>
       <c r="BX3">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
       <c r="BY3">
-        <v>-4.3</v>
+        <v>-5</v>
       </c>
       <c r="BZ3">
-        <v>-5.7</v>
+        <v>-6.3</v>
       </c>
       <c r="CA3">
-        <v>-1.2</v>
+        <v>-1.8</v>
       </c>
       <c r="CB3">
-        <v>-5.4</v>
+        <v>-6.3</v>
       </c>
       <c r="CC3">
-        <v>-7.3</v>
+        <v>-8.1</v>
       </c>
       <c r="CD3">
-        <v>-1.4</v>
+        <v>-2.1</v>
       </c>
       <c r="CE3">
-        <v>-6</v>
+        <v>-7.1</v>
       </c>
       <c r="CF3">
-        <v>-8.199999999999999</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="CG3">
-        <v>-1.6</v>
+        <v>-2.4</v>
       </c>
       <c r="CH3">
-        <v>-6.7</v>
+        <v>-7.9</v>
       </c>
       <c r="CI3">
-        <v>-9.300000000000001</v>
+        <v>-10.4</v>
       </c>
       <c r="CJ3">
-        <v>-1.7</v>
+        <v>-2.5</v>
       </c>
       <c r="CK3">
-        <v>-7.1</v>
+        <v>-8.4</v>
       </c>
       <c r="CL3">
-        <v>-9.9</v>
+        <v>-11.1</v>
       </c>
       <c r="CM3">
-        <v>-3.2</v>
+        <v>-3.9</v>
       </c>
       <c r="CN3">
-        <v>-4.1</v>
+        <v>-5</v>
       </c>
       <c r="CO3">
-        <v>-4.6</v>
+        <v>-5.6</v>
       </c>
       <c r="CP3">
-        <v>-5.2</v>
+        <v>-6.3</v>
       </c>
       <c r="CQ3">
-        <v>-5.5</v>
+        <v>-6.8</v>
       </c>
       <c r="CR3">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CS3">
-        <v>-4.1</v>
+        <v>-5</v>
       </c>
       <c r="CT3">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="CU3">
-        <v>9.1</v>
+        <v>10.1</v>
       </c>
       <c r="CV3">
-        <v>9.699999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="CW3">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="CX3">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
       <c r="CY3">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="CZ3">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="DA3">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="DB3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="DC3">
-        <v>44.4</v>
+        <v>41.1</v>
       </c>
       <c r="DD3" t="s">
         <v>361</v>
@@ -4495,73 +4542,73 @@
         <v>361</v>
       </c>
       <c r="DF3">
-        <v>88.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="DG3">
-        <v>88.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="DH3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="DI3">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="DJ3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DK3">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="DL3">
-        <v>-1.3</v>
+        <v>-2</v>
       </c>
       <c r="DM3">
-        <v>-7.6</v>
+        <v>-8.5</v>
       </c>
       <c r="DN3">
+        <v>-5.7</v>
+      </c>
+      <c r="DO3">
         <v>-5.5</v>
       </c>
-      <c r="DO3">
-        <v>-4.7</v>
-      </c>
       <c r="DP3">
-        <v>-1.1</v>
+        <v>-1.7</v>
       </c>
       <c r="DQ3">
-        <v>-6.6</v>
+        <v>-7.4</v>
       </c>
       <c r="DR3">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="DS3">
-        <v>-1.3</v>
+        <v>-2</v>
       </c>
       <c r="DT3">
-        <v>-7.6</v>
+        <v>-8.5</v>
       </c>
       <c r="DU3">
-        <v>-5.4</v>
+        <v>-6.4</v>
       </c>
       <c r="DV3">
-        <v>-1.3</v>
+        <v>-1.9</v>
       </c>
       <c r="DW3">
-        <v>-7.3</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="DX3">
-        <v>-5.7</v>
+        <v>-6</v>
       </c>
       <c r="DY3">
-        <v>-4.1</v>
+        <v>-5</v>
       </c>
       <c r="DZ3">
-        <v>-4.1</v>
+        <v>-5</v>
       </c>
       <c r="EA3">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="EB3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="EC3">
         <v>0.9</v>
@@ -4576,13 +4623,13 @@
         <v>0.12</v>
       </c>
       <c r="EG3">
-        <v>1.1998</v>
+        <v>1.1985</v>
       </c>
       <c r="EH3" t="s">
         <v>367</v>
       </c>
       <c r="EI3">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="EJ3" t="s">
         <v>122</v>
@@ -4591,13 +4638,13 @@
         <v>125</v>
       </c>
       <c r="EL3">
-        <v>39.8</v>
+        <v>37.2</v>
       </c>
       <c r="EM3">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="EN3">
-        <v>-12.4</v>
+        <v>-15.1</v>
       </c>
       <c r="EO3">
         <v>-0.5</v>
@@ -4606,46 +4653,46 @@
         <v>0</v>
       </c>
       <c r="EQ3">
-        <v>0.976</v>
+        <v>0.969</v>
       </c>
       <c r="ER3">
-        <v>36.9</v>
+        <v>34.3</v>
       </c>
       <c r="ES3">
-        <v>42.4</v>
+        <v>40.1</v>
       </c>
       <c r="ET3">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="EU3">
         <v>46.1</v>
       </c>
       <c r="EV3">
-        <v>69.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="EW3">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="EX3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="EY3">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="EZ3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="FA3">
+        <v>66</v>
+      </c>
+      <c r="FB3">
         <v>64</v>
       </c>
-      <c r="FB3">
-        <v>65.3</v>
-      </c>
       <c r="FC3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="FD3">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:160">
@@ -4662,43 +4709,43 @@
         <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F4" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G4" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="H4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I4" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J4">
-        <v>431.2</v>
+        <v>24.4</v>
       </c>
       <c r="K4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>5</v>
       </c>
       <c r="M4">
-        <v>1.79</v>
+        <v>1.19</v>
       </c>
       <c r="N4">
-        <v>0.92</v>
+        <v>1.24</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>14.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q4">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -4710,19 +4757,19 @@
         <v>9.5</v>
       </c>
       <c r="U4">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="V4">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="W4">
-        <v>-8.4</v>
+        <v>-7.7</v>
       </c>
       <c r="X4">
-        <v>-6.7</v>
+        <v>-6.5</v>
       </c>
       <c r="Y4">
-        <v>-4.8</v>
+        <v>-5.2</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -4731,58 +4778,58 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>88</v>
+        <v>92.5</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="AE4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AF4">
         <v>-2.3</v>
       </c>
       <c r="AG4">
-        <v>-6</v>
+        <v>-5.8</v>
       </c>
       <c r="AH4">
-        <v>-8.300000000000001</v>
+        <v>-8.1</v>
       </c>
       <c r="AI4">
-        <v>-9.5</v>
+        <v>-9.1</v>
       </c>
       <c r="AJ4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AK4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AM4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AN4">
         <v>1</v>
       </c>
       <c r="AO4">
-        <v>9.9</v>
+        <v>8.5</v>
       </c>
       <c r="AP4">
-        <v>91.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AQ4">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="AR4">
         <v>0.92</v>
       </c>
       <c r="AS4">
-        <v>0.849</v>
+        <v>0.852</v>
       </c>
       <c r="AT4">
         <v>2</v>
@@ -4800,34 +4847,34 @@
         <v>0.3</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA4" t="s">
         <v>128</v>
       </c>
       <c r="BB4">
-        <v>64.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="BC4">
-        <v>61.6</v>
+        <v>61</v>
       </c>
       <c r="BD4">
-        <v>47.1</v>
+        <v>48.2</v>
       </c>
       <c r="BE4">
-        <v>53.7</v>
+        <v>55.4</v>
       </c>
       <c r="BF4">
-        <v>1006.7</v>
+        <v>1006.1</v>
       </c>
       <c r="BG4">
-        <v>1024.7</v>
+        <v>1024.1</v>
       </c>
       <c r="BH4">
-        <v>21.4</v>
+        <v>36.4</v>
       </c>
       <c r="BI4">
         <v>0</v>
@@ -4836,211 +4883,211 @@
         <v>0</v>
       </c>
       <c r="BK4">
-        <v>80.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="BL4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="BM4">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="BN4">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="BO4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BP4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BQ4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BR4">
-        <v>0.137</v>
+        <v>0.136</v>
       </c>
       <c r="BS4">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="BT4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BU4">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="BV4">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="BW4">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="BX4">
-        <v>-2.1</v>
+        <v>-1.9</v>
       </c>
       <c r="BY4">
         <v>-5.5</v>
       </c>
       <c r="BZ4">
-        <v>-6.5</v>
+        <v>-6.6</v>
       </c>
       <c r="CA4">
-        <v>-2.7</v>
+        <v>-2.5</v>
       </c>
       <c r="CB4">
         <v>-7</v>
       </c>
       <c r="CC4">
-        <v>-8.300000000000001</v>
+        <v>-8.5</v>
       </c>
       <c r="CD4">
-        <v>-3.1</v>
+        <v>-2.8</v>
       </c>
       <c r="CE4">
         <v>-7.8</v>
       </c>
       <c r="CF4">
-        <v>-9.4</v>
+        <v>-9.6</v>
       </c>
       <c r="CG4">
+        <v>-3.2</v>
+      </c>
+      <c r="CH4">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="CI4">
+        <v>-10.9</v>
+      </c>
+      <c r="CJ4">
         <v>-3.5</v>
-      </c>
-      <c r="CH4">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="CI4">
-        <v>-10.7</v>
-      </c>
-      <c r="CJ4">
-        <v>-3.8</v>
       </c>
       <c r="CK4">
         <v>-9.300000000000001</v>
       </c>
       <c r="CL4">
-        <v>-11.4</v>
+        <v>-11.7</v>
       </c>
       <c r="CM4">
-        <v>-4.6</v>
+        <v>-4.5</v>
       </c>
       <c r="CN4">
+        <v>-5.7</v>
+      </c>
+      <c r="CO4">
+        <v>-6.5</v>
+      </c>
+      <c r="CP4">
+        <v>-7.3</v>
+      </c>
+      <c r="CQ4">
+        <v>-7.8</v>
+      </c>
+      <c r="CR4">
+        <v>9.6</v>
+      </c>
+      <c r="CS4">
         <v>-5.8</v>
       </c>
-      <c r="CO4">
-        <v>-6.6</v>
-      </c>
-      <c r="CP4">
-        <v>-7.4</v>
-      </c>
-      <c r="CQ4">
-        <v>-7.9</v>
-      </c>
-      <c r="CR4">
-        <v>9.4</v>
-      </c>
-      <c r="CS4">
-        <v>-5.9</v>
-      </c>
       <c r="CT4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CU4">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="CV4">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="CW4">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="CX4">
-        <v>14.8</v>
+        <v>13.7</v>
       </c>
       <c r="CY4">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="CZ4">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="DA4">
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="DB4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="DC4">
-        <v>35</v>
+        <v>36.9</v>
       </c>
       <c r="DD4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="DE4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="DF4">
-        <v>84.5</v>
+        <v>92</v>
       </c>
       <c r="DG4">
-        <v>84.5</v>
+        <v>92</v>
       </c>
       <c r="DH4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="DI4">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="DJ4">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="DK4">
         <v>-7.2</v>
       </c>
       <c r="DL4">
-        <v>-2.9</v>
+        <v>-2.7</v>
       </c>
       <c r="DM4">
-        <v>-8.9</v>
+        <v>-9</v>
       </c>
       <c r="DN4">
-        <v>-5.2</v>
+        <v>-5.5</v>
       </c>
       <c r="DO4">
         <v>-6.1</v>
       </c>
       <c r="DP4">
-        <v>-2.5</v>
+        <v>-2.3</v>
       </c>
       <c r="DQ4">
-        <v>-7.5</v>
+        <v>-7.7</v>
       </c>
       <c r="DR4">
         <v>-7.2</v>
       </c>
       <c r="DS4">
-        <v>-2.9</v>
+        <v>-2.7</v>
       </c>
       <c r="DT4">
-        <v>-8.9</v>
+        <v>-9</v>
       </c>
       <c r="DU4">
-        <v>-7.1</v>
+        <v>-7</v>
       </c>
       <c r="DV4">
-        <v>-2.7</v>
+        <v>-2.5</v>
       </c>
       <c r="DW4">
-        <v>-8.4</v>
+        <v>-8.6</v>
       </c>
       <c r="DX4">
-        <v>-5.4</v>
+        <v>-5.7</v>
       </c>
       <c r="DY4">
-        <v>-5.9</v>
+        <v>-5.8</v>
       </c>
       <c r="DZ4">
-        <v>-5.9</v>
+        <v>-5.8</v>
       </c>
       <c r="EA4">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="EB4">
         <v>0.9</v>
@@ -5058,13 +5105,13 @@
         <v>0.12</v>
       </c>
       <c r="EG4">
-        <v>1.1984</v>
+        <v>1.1969</v>
       </c>
       <c r="EH4" t="s">
         <v>367</v>
       </c>
       <c r="EI4">
-        <v>612</v>
+        <v>649</v>
       </c>
       <c r="EJ4" t="s">
         <v>122</v>
@@ -5073,61 +5120,61 @@
         <v>125</v>
       </c>
       <c r="EL4">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="EM4">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="EN4">
-        <v>-17.6</v>
+        <v>-17.4</v>
       </c>
       <c r="EO4">
-        <v>-0.7</v>
+        <v>-0.6</v>
       </c>
       <c r="EP4">
         <v>0</v>
       </c>
       <c r="EQ4">
-        <v>0.963</v>
+        <v>0.964</v>
       </c>
       <c r="ER4">
-        <v>32.2</v>
+        <v>32.5</v>
       </c>
       <c r="ES4">
-        <v>37.3</v>
+        <v>37.9</v>
       </c>
       <c r="ET4">
-        <v>49.5</v>
+        <v>49.8</v>
       </c>
       <c r="EU4">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
       <c r="EV4">
-        <v>69.40000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="EW4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="EX4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="EY4">
-        <v>7.1</v>
+        <v>3.9</v>
       </c>
       <c r="EZ4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="FA4">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="FB4">
-        <v>65.2</v>
+        <v>64.2</v>
       </c>
       <c r="FC4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="FD4">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:160">
@@ -5144,43 +5191,43 @@
         <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G5" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="H5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J5">
-        <v>431.2</v>
+        <v>24.4</v>
       </c>
       <c r="K5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="M5">
-        <v>2.3</v>
+        <v>1.59</v>
       </c>
       <c r="N5">
-        <v>1.56</v>
+        <v>2.38</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>8.9</v>
+        <v>1.7</v>
       </c>
       <c r="Q5">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -5189,22 +5236,22 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="U5">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="V5">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="W5">
-        <v>-7.6</v>
+        <v>-7</v>
       </c>
       <c r="X5">
-        <v>-6.2</v>
+        <v>-6</v>
       </c>
       <c r="Y5">
-        <v>-4.6</v>
+        <v>-4.9</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -5213,58 +5260,58 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>83.8</v>
+        <v>88.2</v>
       </c>
       <c r="AC5">
         <v>0</v>
       </c>
       <c r="AD5">
-        <v>97.5</v>
+        <v>98.2</v>
       </c>
       <c r="AE5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AF5">
         <v>-2.1</v>
       </c>
       <c r="AG5">
-        <v>-5.5</v>
+        <v>-5.4</v>
       </c>
       <c r="AH5">
-        <v>-7.7</v>
+        <v>-7.5</v>
       </c>
       <c r="AI5">
-        <v>-8.699999999999999</v>
+        <v>-8.5</v>
       </c>
       <c r="AJ5" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AK5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AM5" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AN5">
         <v>1</v>
       </c>
       <c r="AO5">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="AP5">
-        <v>91.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="AQ5">
-        <v>37.1</v>
+        <v>37.6</v>
       </c>
       <c r="AR5">
         <v>0.92</v>
       </c>
       <c r="AS5">
-        <v>0.858</v>
+        <v>0.86</v>
       </c>
       <c r="AT5">
         <v>2</v>
@@ -5282,34 +5329,34 @@
         <v>0.3</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA5" t="s">
         <v>128</v>
       </c>
       <c r="BB5">
-        <v>65.09999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="BC5">
-        <v>61.9</v>
+        <v>60.9</v>
       </c>
       <c r="BD5">
-        <v>46.7</v>
+        <v>47.4</v>
       </c>
       <c r="BE5">
-        <v>53.8</v>
+        <v>54.2</v>
       </c>
       <c r="BF5">
-        <v>1006.4</v>
+        <v>1005.6</v>
       </c>
       <c r="BG5">
-        <v>1024.3</v>
+        <v>1023.5</v>
       </c>
       <c r="BH5">
-        <v>14.6</v>
+        <v>32.1</v>
       </c>
       <c r="BI5">
         <v>0</v>
@@ -5318,211 +5365,211 @@
         <v>0</v>
       </c>
       <c r="BK5">
-        <v>93.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="BL5">
         <v>2</v>
       </c>
       <c r="BM5">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="BN5">
         <v>7.7</v>
       </c>
       <c r="BO5">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="BP5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BQ5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BR5">
-        <v>0.136</v>
+        <v>0.135</v>
       </c>
       <c r="BS5">
         <v>7.7</v>
       </c>
       <c r="BT5">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="BU5">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="BV5">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="BW5">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="BX5">
-        <v>-1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="BY5">
-        <v>-5.3</v>
+        <v>-5.2</v>
       </c>
       <c r="BZ5">
         <v>-6.6</v>
       </c>
       <c r="CA5">
-        <v>-2.1</v>
+        <v>-2</v>
       </c>
       <c r="CB5">
-        <v>-6.8</v>
+        <v>-6.6</v>
       </c>
       <c r="CC5">
-        <v>-8.5</v>
+        <v>-8.4</v>
       </c>
       <c r="CD5">
-        <v>-2.4</v>
+        <v>-2.2</v>
       </c>
       <c r="CE5">
-        <v>-7.5</v>
+        <v>-7.4</v>
       </c>
       <c r="CF5">
-        <v>-9.6</v>
+        <v>-9.5</v>
       </c>
       <c r="CG5">
-        <v>-2.8</v>
+        <v>-2.6</v>
       </c>
       <c r="CH5">
-        <v>-8.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="CI5">
-        <v>-10.9</v>
+        <v>-10.8</v>
       </c>
       <c r="CJ5">
-        <v>-3</v>
+        <v>-2.7</v>
       </c>
       <c r="CK5">
-        <v>-9</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="CL5">
-        <v>-11.6</v>
+        <v>-11.5</v>
       </c>
       <c r="CM5">
-        <v>-4.2</v>
+        <v>-4.1</v>
       </c>
       <c r="CN5">
-        <v>-5.4</v>
+        <v>-5.2</v>
       </c>
       <c r="CO5">
-        <v>-6.1</v>
+        <v>-5.9</v>
       </c>
       <c r="CP5">
-        <v>-6.9</v>
+        <v>-6.7</v>
       </c>
       <c r="CQ5">
-        <v>-7.3</v>
+        <v>-7.1</v>
       </c>
       <c r="CR5">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="CS5">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
       <c r="CT5">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="CU5">
         <v>10.5</v>
       </c>
       <c r="CV5">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="CW5">
         <v>7.7</v>
       </c>
       <c r="CX5">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="CY5">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="CZ5">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="DA5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="DB5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="DC5">
-        <v>39.6</v>
+        <v>40.6</v>
       </c>
       <c r="DD5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="DE5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="DF5">
-        <v>89.3</v>
+        <v>94.5</v>
       </c>
       <c r="DG5">
-        <v>89.3</v>
+        <v>94.5</v>
       </c>
       <c r="DH5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="DI5">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="DJ5">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="DK5">
-        <v>-6.9</v>
+        <v>-6.7</v>
       </c>
       <c r="DL5">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="DM5">
-        <v>-9</v>
+        <v>-8.9</v>
       </c>
       <c r="DN5">
+        <v>-5.9</v>
+      </c>
+      <c r="DO5">
         <v>-5.8</v>
       </c>
-      <c r="DO5">
-        <v>-5.9</v>
-      </c>
       <c r="DP5">
+        <v>-1.8</v>
+      </c>
+      <c r="DQ5">
+        <v>-7.6</v>
+      </c>
+      <c r="DR5">
+        <v>-6.7</v>
+      </c>
+      <c r="DS5">
+        <v>-2.1</v>
+      </c>
+      <c r="DT5">
+        <v>-8.9</v>
+      </c>
+      <c r="DU5">
+        <v>-6.7</v>
+      </c>
+      <c r="DV5">
         <v>-2</v>
       </c>
-      <c r="DQ5">
-        <v>-7.7</v>
-      </c>
-      <c r="DR5">
-        <v>-6.9</v>
-      </c>
-      <c r="DS5">
-        <v>-2.3</v>
-      </c>
-      <c r="DT5">
-        <v>-9</v>
-      </c>
-      <c r="DU5">
-        <v>-6.8</v>
-      </c>
-      <c r="DV5">
-        <v>-2.2</v>
-      </c>
       <c r="DW5">
-        <v>-8.6</v>
+        <v>-8.5</v>
       </c>
       <c r="DX5">
         <v>-6.1</v>
       </c>
       <c r="DY5">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
       <c r="DZ5">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
       <c r="EA5">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="EB5">
         <v>0.9</v>
@@ -5540,13 +5587,13 @@
         <v>0.12</v>
       </c>
       <c r="EG5">
-        <v>1.1976</v>
+        <v>1.1962</v>
       </c>
       <c r="EH5" t="s">
         <v>367</v>
       </c>
       <c r="EI5">
-        <v>637</v>
+        <v>673</v>
       </c>
       <c r="EJ5" t="s">
         <v>122</v>
@@ -5555,13 +5602,13 @@
         <v>125</v>
       </c>
       <c r="EL5">
-        <v>35.9</v>
+        <v>36.5</v>
       </c>
       <c r="EM5">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="EN5">
-        <v>-16.4</v>
+        <v>-15.9</v>
       </c>
       <c r="EO5">
         <v>-0.6</v>
@@ -5570,46 +5617,46 @@
         <v>0</v>
       </c>
       <c r="EQ5">
-        <v>0.966</v>
+        <v>0.968</v>
       </c>
       <c r="ER5">
-        <v>33.1</v>
+        <v>33.6</v>
       </c>
       <c r="ES5">
-        <v>38.9</v>
+        <v>39.5</v>
       </c>
       <c r="ET5">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="EU5">
-        <v>45.6</v>
+        <v>45.8</v>
       </c>
       <c r="EV5">
-        <v>69.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="EW5">
         <v>0</v>
       </c>
       <c r="EX5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="EY5">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="EZ5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="FA5">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="FB5">
-        <v>65.59999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="FC5">
         <v>9</v>
       </c>
       <c r="FD5">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6" spans="1:160">
@@ -5626,43 +5673,43 @@
         <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F6" t="s">
         <v>115</v>
       </c>
       <c r="G6" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I6" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J6">
-        <v>266.3</v>
+        <v>50</v>
       </c>
       <c r="K6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="N6">
-        <v>3.01</v>
+        <v>2.79</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>7.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q6">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -5671,25 +5718,25 @@
         <v>0</v>
       </c>
       <c r="T6">
+        <v>4.2</v>
+      </c>
+      <c r="U6">
+        <v>6.1</v>
+      </c>
+      <c r="V6">
+        <v>8.6</v>
+      </c>
+      <c r="W6">
+        <v>2.9</v>
+      </c>
+      <c r="X6">
         <v>4.1</v>
       </c>
-      <c r="U6">
-        <v>5.9</v>
-      </c>
-      <c r="V6">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W6">
-        <v>2.7</v>
-      </c>
-      <c r="X6">
-        <v>3.9</v>
-      </c>
       <c r="Y6">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="Z6">
-        <v>19.9</v>
+        <v>24.4</v>
       </c>
       <c r="AA6">
         <v>0</v>
@@ -5701,52 +5748,52 @@
         <v>100</v>
       </c>
       <c r="AD6">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="AE6" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AF6">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG6">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AH6">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AI6">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AJ6" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AK6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AM6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AN6">
         <v>1</v>
       </c>
       <c r="AO6">
-        <v>15.8</v>
+        <v>14.3</v>
       </c>
       <c r="AP6">
-        <v>85.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AQ6">
-        <v>66.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="AR6">
         <v>0.78</v>
       </c>
       <c r="AS6">
-        <v>0.8179999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="AT6">
         <v>8</v>
@@ -5764,76 +5811,76 @@
         <v>0.8</v>
       </c>
       <c r="AY6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA6" t="s">
         <v>129</v>
       </c>
       <c r="BB6">
-        <v>101.2</v>
+        <v>102.6</v>
       </c>
       <c r="BC6">
-        <v>103.3</v>
+        <v>103.5</v>
       </c>
       <c r="BD6">
-        <v>47.5</v>
+        <v>49.9</v>
       </c>
       <c r="BE6">
-        <v>17.2</v>
+        <v>18</v>
       </c>
       <c r="BF6">
-        <v>992.3</v>
+        <v>991</v>
       </c>
       <c r="BG6">
-        <v>1009.9</v>
+        <v>1008.6</v>
       </c>
       <c r="BH6">
-        <v>37.7</v>
+        <v>0</v>
       </c>
       <c r="BI6">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="BJ6">
         <v>0</v>
       </c>
       <c r="BK6">
-        <v>173.5</v>
+        <v>163.5</v>
       </c>
       <c r="BL6">
         <v>2</v>
       </c>
       <c r="BM6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BN6">
         <v>2.9</v>
       </c>
       <c r="BO6">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BQ6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BR6">
-        <v>0.14</v>
+        <v>0.141</v>
       </c>
       <c r="BS6">
         <v>2.9</v>
       </c>
       <c r="BT6">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BU6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BW6">
         <v>4.7</v>
@@ -5845,169 +5892,169 @@
         <v>2.2</v>
       </c>
       <c r="BZ6">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="CA6">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="CB6">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="CC6">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="CD6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="CE6">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="CF6">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="CG6">
         <v>4.1</v>
       </c>
       <c r="CH6">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="CI6">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="CJ6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="CK6">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="CL6">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="CM6">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="CN6">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="CO6">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="CP6">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="CQ6">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="CR6">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="CS6">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="CT6">
         <v>3.8</v>
       </c>
       <c r="CU6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="CV6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CW6">
         <v>2.9</v>
       </c>
       <c r="CX6">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="CY6">
-        <v>10.7</v>
+        <v>11.2</v>
       </c>
       <c r="CZ6">
-        <v>10.7</v>
+        <v>11.2</v>
       </c>
       <c r="DA6">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DB6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="DC6">
-        <v>177.9</v>
+        <v>179.4</v>
       </c>
       <c r="DD6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="DE6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="DF6">
-        <v>74</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="DG6">
-        <v>74</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="DH6">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="DI6">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="DJ6">
-        <v>14</v>
+        <v>18.8</v>
       </c>
       <c r="DK6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="DL6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="DM6">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="DN6">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="DO6">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="DP6">
         <v>2.9</v>
       </c>
       <c r="DQ6">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="DR6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="DS6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="DT6">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="DU6">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="DV6">
         <v>3.1</v>
       </c>
       <c r="DW6">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="DX6">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="DY6">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DZ6">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="EA6">
         <v>0.95</v>
       </c>
       <c r="EB6">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="EC6">
         <v>0.85</v>
@@ -6022,13 +6069,13 @@
         <v>0.12</v>
       </c>
       <c r="EG6">
-        <v>1.1047</v>
+        <v>1.1001</v>
       </c>
       <c r="EH6" t="s">
         <v>368</v>
       </c>
       <c r="EI6">
-        <v>3496</v>
+        <v>3634</v>
       </c>
       <c r="EJ6" t="s">
         <v>122</v>
@@ -6037,13 +6084,13 @@
         <v>125</v>
       </c>
       <c r="EL6">
-        <v>69.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="EM6">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="EN6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="EO6">
         <v>1.3</v>
@@ -6052,46 +6099,46 @@
         <v>0</v>
       </c>
       <c r="EQ6">
-        <v>1.047</v>
+        <v>1.048</v>
       </c>
       <c r="ER6">
-        <v>68.5</v>
+        <v>69.2</v>
       </c>
       <c r="ES6">
-        <v>70</v>
+        <v>70.7</v>
       </c>
       <c r="ET6">
-        <v>59.2</v>
+        <v>59.5</v>
       </c>
       <c r="EU6">
-        <v>55.8</v>
+        <v>56.2</v>
       </c>
       <c r="EV6">
-        <v>40.7</v>
+        <v>39.1</v>
       </c>
       <c r="EW6">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="EY6">
-        <v>13.3</v>
+        <v>2.2</v>
       </c>
       <c r="EZ6" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="FA6">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="FB6">
-        <v>101.7</v>
+        <v>101.2</v>
       </c>
       <c r="FC6">
         <v>5</v>
       </c>
       <c r="FD6">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="7" spans="1:160">
@@ -6108,43 +6155,43 @@
         <v>119</v>
       </c>
       <c r="E7" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F7" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G7" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H7" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I7" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J7">
-        <v>266.3</v>
+        <v>50</v>
       </c>
       <c r="K7">
-        <v>18</v>
+        <v>0.8</v>
       </c>
       <c r="L7">
         <v>5</v>
       </c>
       <c r="M7">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="N7">
-        <v>2.86</v>
+        <v>3.18</v>
       </c>
       <c r="O7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>14</v>
+        <v>9.5</v>
       </c>
       <c r="Q7">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -6153,25 +6200,25 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="U7">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="V7">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="W7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="X7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="Z7">
-        <v>59.6</v>
+        <v>64</v>
       </c>
       <c r="AA7">
         <v>0</v>
@@ -6183,52 +6230,52 @@
         <v>100</v>
       </c>
       <c r="AD7">
-        <v>97.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="AE7" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AF7">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AH7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AI7">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="AJ7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AK7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL7" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AM7" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AN7">
         <v>1</v>
       </c>
       <c r="AO7">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="AP7">
-        <v>88</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="AQ7">
-        <v>70.2</v>
+        <v>71.3</v>
       </c>
       <c r="AR7">
         <v>0.78</v>
       </c>
       <c r="AS7">
-        <v>0.8120000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="AT7">
         <v>10</v>
@@ -6249,79 +6296,79 @@
         <v>0</v>
       </c>
       <c r="AZ7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BB7">
-        <v>103.2</v>
+        <v>104</v>
       </c>
       <c r="BC7">
-        <v>104.1</v>
+        <v>104.6</v>
       </c>
       <c r="BD7">
-        <v>47.5</v>
+        <v>50.2</v>
       </c>
       <c r="BE7">
-        <v>16.6</v>
+        <v>17.7</v>
       </c>
       <c r="BF7">
-        <v>991.7</v>
+        <v>990.8</v>
       </c>
       <c r="BG7">
-        <v>1009.2</v>
+        <v>1008.3</v>
       </c>
       <c r="BH7">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="BI7">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="BJ7">
         <v>0</v>
       </c>
       <c r="BK7">
-        <v>180.4</v>
+        <v>169</v>
       </c>
       <c r="BL7">
         <v>2</v>
       </c>
       <c r="BM7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN7">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BO7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BQ7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BR7">
         <v>0.141</v>
       </c>
       <c r="BS7">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BT7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BU7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV7">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BW7">
         <v>6.2</v>
       </c>
       <c r="BX7">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BY7">
         <v>3.2</v>
@@ -6330,40 +6377,40 @@
         <v>2.9</v>
       </c>
       <c r="CA7">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="CB7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="CC7">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="CD7">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="CE7">
         <v>4.7</v>
       </c>
       <c r="CF7">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="CG7">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="CH7">
         <v>5.4</v>
       </c>
       <c r="CI7">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CJ7">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="CK7">
         <v>5.8</v>
       </c>
       <c r="CL7">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="CM7">
         <v>2.8</v>
@@ -6381,7 +6428,7 @@
         <v>5.2</v>
       </c>
       <c r="CR7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="CS7">
         <v>3.7</v>
@@ -6396,88 +6443,88 @@
         <v>5.7</v>
       </c>
       <c r="CW7">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="CX7">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="CY7">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="CZ7">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="DA7">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DB7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="DC7">
-        <v>218.2</v>
+        <v>220.4</v>
       </c>
       <c r="DD7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="DE7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="DF7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="DG7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="DH7">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="DI7">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="DJ7">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="DK7">
         <v>4.6</v>
       </c>
       <c r="DL7">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="DM7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="DN7">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="DO7">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="DP7">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DQ7">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="DR7">
         <v>4.6</v>
       </c>
       <c r="DS7">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="DT7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="DU7">
         <v>4.2</v>
       </c>
       <c r="DV7">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="DW7">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="DX7">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="DY7">
         <v>3.7</v>
@@ -6504,13 +6551,13 @@
         <v>0.12</v>
       </c>
       <c r="EG7">
-        <v>1.1002</v>
+        <v>1.097</v>
       </c>
       <c r="EH7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="EI7">
-        <v>3648</v>
+        <v>3734</v>
       </c>
       <c r="EJ7" t="s">
         <v>122</v>
@@ -6519,55 +6566,55 @@
         <v>125</v>
       </c>
       <c r="EL7">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="EM7">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="EN7">
         <v>9.1</v>
       </c>
       <c r="EO7">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="EP7">
         <v>0</v>
       </c>
       <c r="EQ7">
-        <v>1.055</v>
+        <v>1.056</v>
       </c>
       <c r="ER7">
-        <v>73.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="ES7">
-        <v>72.2</v>
+        <v>72.5</v>
       </c>
       <c r="ET7">
-        <v>60.1</v>
+        <v>60.3</v>
       </c>
       <c r="EU7">
-        <v>56.7</v>
+        <v>57.1</v>
       </c>
       <c r="EV7">
-        <v>38.5</v>
+        <v>37.6</v>
       </c>
       <c r="EW7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="EY7">
-        <v>8.1</v>
+        <v>2.6</v>
       </c>
       <c r="EZ7" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="FA7">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="FB7">
-        <v>102.9</v>
+        <v>102.1</v>
       </c>
       <c r="FC7">
         <v>5</v>
@@ -6590,43 +6637,43 @@
         <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F8" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H8" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I8" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J8">
-        <v>266.3</v>
+        <v>50</v>
       </c>
       <c r="K8">
-        <v>19</v>
+        <v>1.8</v>
       </c>
       <c r="L8">
         <v>5</v>
       </c>
       <c r="M8">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="N8">
-        <v>2.87</v>
+        <v>3.72</v>
       </c>
       <c r="O8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>13.4</v>
+        <v>23.4</v>
       </c>
       <c r="Q8">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -6635,25 +6682,25 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="U8">
+        <v>7</v>
+      </c>
+      <c r="V8">
+        <v>9.4</v>
+      </c>
+      <c r="W8">
+        <v>3.7</v>
+      </c>
+      <c r="X8">
+        <v>5.1</v>
+      </c>
+      <c r="Y8">
         <v>7.1</v>
       </c>
-      <c r="V8">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W8">
-        <v>4</v>
-      </c>
-      <c r="X8">
-        <v>5.3</v>
-      </c>
-      <c r="Y8">
-        <v>6.9</v>
-      </c>
       <c r="Z8">
-        <v>58.7</v>
+        <v>53.5</v>
       </c>
       <c r="AA8">
         <v>0</v>
@@ -6665,52 +6712,52 @@
         <v>100</v>
       </c>
       <c r="AD8">
-        <v>97.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AE8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AF8">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG8">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AH8">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="AI8">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="AJ8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AK8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL8" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AM8" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AN8">
         <v>1</v>
       </c>
       <c r="AO8">
-        <v>17.9</v>
+        <v>20.2</v>
       </c>
       <c r="AP8">
-        <v>87.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="AQ8">
-        <v>70.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="AR8">
         <v>0.78</v>
       </c>
       <c r="AS8">
-        <v>0.8139999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="AT8">
         <v>10</v>
@@ -6731,244 +6778,244 @@
         <v>0</v>
       </c>
       <c r="AZ8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BB8">
-        <v>103.2</v>
+        <v>104.1</v>
       </c>
       <c r="BC8">
-        <v>103.7</v>
+        <v>104.6</v>
       </c>
       <c r="BD8">
-        <v>47.7</v>
+        <v>51.1</v>
       </c>
       <c r="BE8">
-        <v>16.8</v>
+        <v>18.5</v>
       </c>
       <c r="BF8">
-        <v>991.1</v>
+        <v>990.2</v>
       </c>
       <c r="BG8">
-        <v>1008.5</v>
+        <v>1007.7</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BI8">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="BJ8">
         <v>0</v>
       </c>
       <c r="BK8">
-        <v>183.5</v>
+        <v>174.3</v>
       </c>
       <c r="BL8">
         <v>2</v>
       </c>
       <c r="BM8">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BN8">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BO8">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BP8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BQ8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BR8">
         <v>0.141</v>
       </c>
       <c r="BS8">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BT8">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BU8">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV8">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BW8">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="BX8">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BY8">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="BZ8">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="CA8">
         <v>2.6</v>
       </c>
       <c r="CB8">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="CC8">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="CD8">
         <v>3</v>
       </c>
       <c r="CE8">
+        <v>4.6</v>
+      </c>
+      <c r="CF8">
+        <v>4.4</v>
+      </c>
+      <c r="CG8">
+        <v>3.4</v>
+      </c>
+      <c r="CH8">
+        <v>5.2</v>
+      </c>
+      <c r="CI8">
+        <v>5</v>
+      </c>
+      <c r="CJ8">
+        <v>3.7</v>
+      </c>
+      <c r="CK8">
+        <v>5.6</v>
+      </c>
+      <c r="CL8">
+        <v>5.4</v>
+      </c>
+      <c r="CM8">
+        <v>2.7</v>
+      </c>
+      <c r="CN8">
+        <v>3.6</v>
+      </c>
+      <c r="CO8">
+        <v>4.1</v>
+      </c>
+      <c r="CP8">
+        <v>4.7</v>
+      </c>
+      <c r="CQ8">
+        <v>5</v>
+      </c>
+      <c r="CR8">
+        <v>4.7</v>
+      </c>
+      <c r="CS8">
+        <v>3.6</v>
+      </c>
+      <c r="CT8">
         <v>4.9</v>
       </c>
-      <c r="CF8">
-        <v>4.8</v>
-      </c>
-      <c r="CG8">
-        <v>3.5</v>
-      </c>
-      <c r="CH8">
+      <c r="CU8">
+        <v>5.2</v>
+      </c>
+      <c r="CV8">
         <v>5.6</v>
       </c>
-      <c r="CI8">
-        <v>5.5</v>
-      </c>
-      <c r="CJ8">
+      <c r="CW8">
         <v>3.8</v>
       </c>
-      <c r="CK8">
-        <v>6</v>
-      </c>
-      <c r="CL8">
-        <v>5.9</v>
-      </c>
-      <c r="CM8">
-        <v>2.9</v>
-      </c>
-      <c r="CN8">
-        <v>3.8</v>
-      </c>
-      <c r="CO8">
-        <v>4.3</v>
-      </c>
-      <c r="CP8">
-        <v>4.9</v>
-      </c>
-      <c r="CQ8">
-        <v>5.3</v>
-      </c>
-      <c r="CR8">
-        <v>5.1</v>
-      </c>
-      <c r="CS8">
-        <v>3.8</v>
-      </c>
-      <c r="CT8">
-        <v>5.3</v>
-      </c>
-      <c r="CU8">
-        <v>5.6</v>
-      </c>
-      <c r="CV8">
-        <v>6</v>
-      </c>
-      <c r="CW8">
-        <v>4.1</v>
-      </c>
       <c r="CX8">
-        <v>14.5</v>
+        <v>15.2</v>
       </c>
       <c r="CY8">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="CZ8">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
       <c r="DA8">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
       <c r="DB8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="DC8">
-        <v>223.9</v>
+        <v>221.6</v>
       </c>
       <c r="DD8" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="DE8" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="DF8">
-        <v>87.8</v>
+        <v>80.8</v>
       </c>
       <c r="DG8">
-        <v>87.8</v>
+        <v>80.8</v>
       </c>
       <c r="DH8">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="DI8">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="DJ8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DK8">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="DL8">
         <v>3</v>
       </c>
       <c r="DM8">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="DN8">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="DO8">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="DP8">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DQ8">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="DR8">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="DS8">
         <v>3</v>
       </c>
       <c r="DT8">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="DU8">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="DV8">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="DW8">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="DX8">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="DY8">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="DZ8">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="EA8">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="EB8">
         <v>0.5</v>
@@ -6986,13 +7033,13 @@
         <v>0.12</v>
       </c>
       <c r="EG8">
-        <v>1.0994</v>
+        <v>1.0961</v>
       </c>
       <c r="EH8" t="s">
         <v>369</v>
       </c>
       <c r="EI8">
-        <v>3672</v>
+        <v>3759</v>
       </c>
       <c r="EJ8" t="s">
         <v>122</v>
@@ -7001,16 +7048,16 @@
         <v>125</v>
       </c>
       <c r="EL8">
-        <v>73.3</v>
+        <v>73.2</v>
       </c>
       <c r="EM8">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="EN8">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="EO8">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="EP8">
         <v>0</v>
@@ -7019,43 +7066,43 @@
         <v>1.056</v>
       </c>
       <c r="ER8">
-        <v>73.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="ES8">
-        <v>72.2</v>
+        <v>72.3</v>
       </c>
       <c r="ET8">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="EU8">
-        <v>56.8</v>
+        <v>57.1</v>
       </c>
       <c r="EV8">
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
       <c r="EW8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="EY8">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="EZ8" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="FA8">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="FB8">
-        <v>102.9</v>
+        <v>102.3</v>
       </c>
       <c r="FC8">
         <v>5</v>
       </c>
       <c r="FD8">
-        <v>5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="9" spans="1:160">
@@ -7072,43 +7119,43 @@
         <v>119</v>
       </c>
       <c r="E9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F9" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G9" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H9" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I9" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J9">
-        <v>266.3</v>
+        <v>50</v>
       </c>
       <c r="K9">
-        <v>20</v>
+        <v>2.8</v>
       </c>
       <c r="L9">
         <v>5</v>
       </c>
       <c r="M9">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
       <c r="N9">
-        <v>1.61</v>
+        <v>2.08</v>
       </c>
       <c r="O9">
         <v>0.5</v>
       </c>
       <c r="P9">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -7117,28 +7164,28 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="U9">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="V9">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="W9">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="Y9">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z9">
-        <v>99.09999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AA9">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="AB9">
         <v>0</v>
@@ -7147,55 +7194,55 @@
         <v>100</v>
       </c>
       <c r="AD9">
-        <v>97.7</v>
+        <v>97.3</v>
       </c>
       <c r="AE9" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AF9">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AG9">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="AH9">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AI9">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="AJ9" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AK9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AM9" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AN9">
         <v>1</v>
       </c>
       <c r="AO9">
-        <v>9.199999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="AP9">
-        <v>84.90000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="AQ9">
-        <v>73.5</v>
+        <v>74.7</v>
       </c>
       <c r="AR9">
         <v>0.78</v>
       </c>
       <c r="AS9">
-        <v>0.8179999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="AT9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU9">
         <v>0</v>
@@ -7213,244 +7260,244 @@
         <v>0</v>
       </c>
       <c r="AZ9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BB9">
-        <v>101.4</v>
+        <v>100</v>
       </c>
       <c r="BC9">
-        <v>93.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="BD9">
-        <v>52</v>
+        <v>52.9</v>
       </c>
       <c r="BE9">
-        <v>21.1</v>
+        <v>21.8</v>
       </c>
       <c r="BF9">
-        <v>990.6</v>
+        <v>990</v>
       </c>
       <c r="BG9">
-        <v>1008.2</v>
+        <v>1007.6</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="BI9">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="BJ9">
         <v>0</v>
       </c>
       <c r="BK9">
-        <v>153.5</v>
+        <v>138.2</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BM9">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN9">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="BO9">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BP9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BQ9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BR9">
-        <v>0.14</v>
+        <v>0.141</v>
       </c>
       <c r="BS9">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="BT9">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU9">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BV9">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="BW9">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="BX9">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="BY9">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BZ9">
         <v>5.6</v>
       </c>
       <c r="CA9">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="CB9">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CC9">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="CD9">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="CE9">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="CF9">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="CG9">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="CH9">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="CI9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CJ9">
+        <v>5.4</v>
+      </c>
+      <c r="CK9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CL9">
+        <v>10.6</v>
+      </c>
+      <c r="CM9">
+        <v>4.6</v>
+      </c>
+      <c r="CN9">
+        <v>6.1</v>
+      </c>
+      <c r="CO9">
+        <v>7</v>
+      </c>
+      <c r="CP9">
+        <v>8</v>
+      </c>
+      <c r="CQ9">
+        <v>8.6</v>
+      </c>
+      <c r="CR9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CS9">
+        <v>6.2</v>
+      </c>
+      <c r="CT9">
+        <v>9.1</v>
+      </c>
+      <c r="CU9">
         <v>9.699999999999999</v>
       </c>
-      <c r="CJ9">
-        <v>4.4</v>
-      </c>
-      <c r="CK9">
-        <v>9.1</v>
-      </c>
-      <c r="CL9">
-        <v>10.5</v>
-      </c>
-      <c r="CM9">
-        <v>4.3</v>
-      </c>
-      <c r="CN9">
-        <v>5.6</v>
-      </c>
-      <c r="CO9">
-        <v>6.4</v>
-      </c>
-      <c r="CP9">
-        <v>7.4</v>
-      </c>
-      <c r="CQ9">
-        <v>7.9</v>
-      </c>
-      <c r="CR9">
-        <v>8.6</v>
-      </c>
-      <c r="CS9">
-        <v>5.7</v>
-      </c>
-      <c r="CT9">
-        <v>9</v>
-      </c>
-      <c r="CU9">
-        <v>9.5</v>
-      </c>
       <c r="CV9">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="CW9">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="CX9">
-        <v>18.9</v>
+        <v>20.2</v>
       </c>
       <c r="CY9">
-        <v>14.8</v>
+        <v>15.7</v>
       </c>
       <c r="CZ9">
-        <v>14.8</v>
+        <v>15.7</v>
       </c>
       <c r="DA9">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DB9" t="s">
         <v>356</v>
       </c>
       <c r="DC9">
-        <v>236.5</v>
+        <v>231.2</v>
       </c>
       <c r="DD9" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="DE9" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="DF9">
-        <v>95</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="DG9">
-        <v>95</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="DH9">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="DI9">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="DJ9">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="DK9">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="DL9">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="DM9">
         <v>8.4</v>
       </c>
       <c r="DN9">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="DO9">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="DP9">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="DQ9">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="DR9">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="DS9">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="DT9">
         <v>8.4</v>
       </c>
       <c r="DU9">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="DV9">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="DW9">
         <v>7.5</v>
       </c>
       <c r="DX9">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="DY9">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="DZ9">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="EA9">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="EB9">
         <v>0.8</v>
@@ -7468,13 +7515,13 @@
         <v>0.12</v>
       </c>
       <c r="EG9">
-        <v>1.1016</v>
+        <v>1.1035</v>
       </c>
       <c r="EH9" t="s">
         <v>368</v>
       </c>
       <c r="EI9">
-        <v>3568</v>
+        <v>3495</v>
       </c>
       <c r="EJ9" t="s">
         <v>122</v>
@@ -7483,61 +7530,61 @@
         <v>125</v>
       </c>
       <c r="EL9">
-        <v>77.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="EM9">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="EN9">
-        <v>13.9</v>
+        <v>15.2</v>
       </c>
       <c r="EO9">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="EP9">
         <v>0</v>
       </c>
       <c r="EQ9">
-        <v>1.066</v>
+        <v>1.069</v>
       </c>
       <c r="ER9">
-        <v>79.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="ES9">
-        <v>75.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="ET9">
-        <v>63.6</v>
+        <v>63.5</v>
       </c>
       <c r="EU9">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
       <c r="EV9">
-        <v>40.5</v>
+        <v>41.4</v>
       </c>
       <c r="EW9">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="EX9" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="EY9">
-        <v>19.9</v>
+        <v>17.9</v>
       </c>
       <c r="EZ9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="FA9">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="FB9">
-        <v>98.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="FC9">
         <v>5</v>
       </c>
       <c r="FD9">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="10" spans="1:160">
@@ -7554,40 +7601,40 @@
         <v>120</v>
       </c>
       <c r="E10" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F10" t="s">
         <v>116</v>
       </c>
       <c r="G10" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H10" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J10">
-        <v>405.9</v>
+        <v>74.5</v>
       </c>
       <c r="K10">
-        <v>19.5</v>
+        <v>2.3</v>
       </c>
       <c r="L10">
         <v>5</v>
       </c>
       <c r="M10">
-        <v>1.26</v>
+        <v>2.54</v>
       </c>
       <c r="N10">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="O10">
-        <v>2.77</v>
+        <v>18.9</v>
       </c>
       <c r="P10">
-        <v>92.5</v>
+        <v>72</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -7623,7 +7670,7 @@
         <v>100</v>
       </c>
       <c r="AE10" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AF10">
         <v>0</v>
@@ -7638,28 +7685,28 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AK10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AM10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AN10">
         <v>0.5</v>
       </c>
       <c r="AO10">
-        <v>11.8</v>
+        <v>20.8</v>
       </c>
       <c r="AP10">
-        <v>85.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AQ10">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -7668,7 +7715,7 @@
         <v>0.35</v>
       </c>
       <c r="AT10">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AU10">
         <v>0</v>
@@ -7683,49 +7730,49 @@
         <v>0</v>
       </c>
       <c r="AY10">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="AZ10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA10" t="s">
         <v>130</v>
       </c>
       <c r="BB10">
-        <v>81.7</v>
+        <v>84.2</v>
       </c>
       <c r="BC10">
-        <v>88.3</v>
+        <v>94.8</v>
       </c>
       <c r="BD10">
         <v>75.59999999999999</v>
       </c>
       <c r="BE10">
-        <v>81.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="BF10">
-        <v>1013.7</v>
+        <v>1014.1</v>
       </c>
       <c r="BG10">
-        <v>1014.9</v>
+        <v>1015.3</v>
       </c>
       <c r="BH10">
-        <v>96.3</v>
+        <v>87.2</v>
       </c>
       <c r="BI10">
-        <v>41.6</v>
+        <v>37.2</v>
       </c>
       <c r="BJ10">
-        <v>0.014</v>
+        <v>0.031</v>
       </c>
       <c r="BK10">
-        <v>37.3</v>
+        <v>45.4</v>
       </c>
       <c r="BL10">
-        <v>1343</v>
+        <v>1846</v>
       </c>
       <c r="BM10">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="BN10">
         <v>0</v>
@@ -7734,10 +7781,10 @@
         <v>0</v>
       </c>
       <c r="BP10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BQ10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BR10">
         <v>0.187</v>
@@ -7758,46 +7805,46 @@
         <v>0</v>
       </c>
       <c r="BX10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BZ10">
         <v>0</v>
       </c>
       <c r="CA10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10">
         <v>0</v>
       </c>
       <c r="CD10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF10">
         <v>0</v>
       </c>
       <c r="CG10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CI10">
         <v>0</v>
       </c>
       <c r="CJ10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL10">
         <v>0</v>
@@ -7836,7 +7883,7 @@
         <v>0</v>
       </c>
       <c r="CX10">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CY10">
         <v>0</v>
@@ -7848,58 +7895,58 @@
         <v>0</v>
       </c>
       <c r="DB10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="DC10">
-        <v>340.3</v>
+        <v>178.5</v>
       </c>
       <c r="DD10" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="DE10" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="DF10">
-        <v>5.3</v>
+        <v>50.4</v>
       </c>
       <c r="DG10">
-        <v>5.3</v>
+        <v>50.4</v>
       </c>
       <c r="DH10">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="DI10">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="DJ10">
-        <v>41.9</v>
+        <v>0</v>
       </c>
       <c r="DK10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10">
         <v>0</v>
       </c>
       <c r="DN10">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ10">
         <v>0</v>
       </c>
       <c r="DR10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DS10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT10">
         <v>0</v>
@@ -7992,25 +8039,25 @@
         <v>0</v>
       </c>
       <c r="EX10" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="EY10">
-        <v>16.9</v>
+        <v>15.5</v>
       </c>
       <c r="EZ10" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="FA10">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="FB10">
-        <v>81.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="FC10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="FD10">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11" spans="1:160">
@@ -8027,25 +8074,25 @@
         <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F11" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G11" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H11" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I11" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J11">
-        <v>405.9</v>
+        <v>74.5</v>
       </c>
       <c r="K11">
-        <v>20.5</v>
+        <v>3.3</v>
       </c>
       <c r="L11">
         <v>5</v>
@@ -8054,13 +8101,13 @@
         <v>1.86</v>
       </c>
       <c r="N11">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="O11">
-        <v>7.55</v>
+        <v>19.5</v>
       </c>
       <c r="P11">
-        <v>24.8</v>
+        <v>98.8</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -8096,7 +8143,7 @@
         <v>100</v>
       </c>
       <c r="AE11" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AF11">
         <v>0</v>
@@ -8111,28 +8158,28 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AK11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AM11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AN11">
         <v>0.5</v>
       </c>
       <c r="AO11">
-        <v>14.7</v>
+        <v>18.2</v>
       </c>
       <c r="AP11">
-        <v>86.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="AQ11">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -8141,64 +8188,64 @@
         <v>0.35</v>
       </c>
       <c r="AT11">
+        <v>7</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
         <v>3</v>
       </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>51</v>
-      </c>
       <c r="AZ11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA11" t="s">
         <v>130</v>
       </c>
       <c r="BB11">
-        <v>79.7</v>
+        <v>81.7</v>
       </c>
       <c r="BC11">
-        <v>85.2</v>
+        <v>93.2</v>
       </c>
       <c r="BD11">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BE11">
-        <v>86.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="BF11">
-        <v>1014.5</v>
+        <v>1014.8</v>
       </c>
       <c r="BG11">
-        <v>1015.7</v>
+        <v>1016</v>
       </c>
       <c r="BH11">
-        <v>96.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="BI11">
-        <v>46.2</v>
+        <v>38.1</v>
       </c>
       <c r="BJ11">
-        <v>0.027</v>
+        <v>0.041</v>
       </c>
       <c r="BK11">
-        <v>34.2</v>
+        <v>35.8</v>
       </c>
       <c r="BL11">
-        <v>830</v>
+        <v>1850</v>
       </c>
       <c r="BM11">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="BN11">
         <v>0</v>
@@ -8207,10 +8254,10 @@
         <v>0</v>
       </c>
       <c r="BP11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BQ11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BR11">
         <v>0.187</v>
@@ -8231,64 +8278,64 @@
         <v>0</v>
       </c>
       <c r="BX11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BZ11">
         <v>-0</v>
       </c>
       <c r="CA11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11">
         <v>-0</v>
       </c>
       <c r="CD11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF11">
         <v>-0</v>
       </c>
       <c r="CG11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CI11">
         <v>-0</v>
       </c>
       <c r="CJ11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11">
         <v>-0</v>
       </c>
       <c r="CM11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CR11">
         <v>0</v>
@@ -8309,7 +8356,7 @@
         <v>0</v>
       </c>
       <c r="CX11">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="CY11">
         <v>0</v>
@@ -8324,34 +8371,34 @@
         <v>357</v>
       </c>
       <c r="DC11">
-        <v>71.09999999999999</v>
+        <v>155.3</v>
       </c>
       <c r="DD11" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="DE11" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="DF11">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="DG11">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="DH11">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="DI11">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="DJ11">
-        <v>3.1</v>
+        <v>38.5</v>
       </c>
       <c r="DK11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11">
         <v>-0</v>
@@ -8360,19 +8407,19 @@
         <v>-0</v>
       </c>
       <c r="DO11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ11">
         <v>-0</v>
       </c>
       <c r="DR11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DS11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT11">
         <v>-0</v>
@@ -8465,25 +8512,25 @@
         <v>0</v>
       </c>
       <c r="EX11" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="EY11">
-        <v>12.8</v>
+        <v>17.8</v>
       </c>
       <c r="EZ11" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="FA11">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="FB11">
-        <v>79.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="FC11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="FD11">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="12" spans="1:160">
@@ -8500,40 +8547,40 @@
         <v>120</v>
       </c>
       <c r="E12" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F12" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G12" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H12" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I12" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J12">
-        <v>405.9</v>
+        <v>74.5</v>
       </c>
       <c r="K12">
-        <v>21.5</v>
+        <v>4.3</v>
       </c>
       <c r="L12">
         <v>5</v>
       </c>
       <c r="M12">
-        <v>1.96</v>
+        <v>1.29</v>
       </c>
       <c r="N12">
-        <v>2.46</v>
+        <v>1.05</v>
       </c>
       <c r="O12">
-        <v>14.65</v>
+        <v>17.71</v>
       </c>
       <c r="P12">
-        <v>8.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -8569,7 +8616,7 @@
         <v>100</v>
       </c>
       <c r="AE12" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AF12">
         <v>0</v>
@@ -8584,28 +8631,28 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AK12" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AM12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AN12">
         <v>0.5</v>
       </c>
       <c r="AO12">
-        <v>20.3</v>
+        <v>14.5</v>
       </c>
       <c r="AP12">
-        <v>83.7</v>
+        <v>84.7</v>
       </c>
       <c r="AQ12">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -8614,7 +8661,7 @@
         <v>0.35</v>
       </c>
       <c r="AT12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU12">
         <v>0</v>
@@ -8629,49 +8676,49 @@
         <v>0</v>
       </c>
       <c r="AY12">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="AZ12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA12" t="s">
-        <v>353</v>
+        <v>130</v>
       </c>
       <c r="BB12">
-        <v>78.59999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="BC12">
-        <v>85.09999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="BD12">
-        <v>75.09999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="BE12">
-        <v>89.3</v>
+        <v>88.7</v>
       </c>
       <c r="BF12">
-        <v>1015.4</v>
+        <v>1015.3</v>
       </c>
       <c r="BG12">
         <v>1016.5</v>
       </c>
       <c r="BH12">
-        <v>96.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="BI12">
-        <v>36.7</v>
+        <v>46.4</v>
       </c>
       <c r="BJ12">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="BK12">
-        <v>28</v>
+        <v>30.5</v>
       </c>
       <c r="BL12">
-        <v>757</v>
+        <v>1568</v>
       </c>
       <c r="BM12">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="BN12">
         <v>0</v>
@@ -8680,10 +8727,10 @@
         <v>0</v>
       </c>
       <c r="BP12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BQ12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BR12">
         <v>0.187</v>
@@ -8782,7 +8829,7 @@
         <v>0</v>
       </c>
       <c r="CX12">
-        <v>10.9</v>
+        <v>8.5</v>
       </c>
       <c r="CY12">
         <v>0</v>
@@ -8794,31 +8841,31 @@
         <v>0</v>
       </c>
       <c r="DB12" t="s">
-        <v>358</v>
+        <v>136</v>
       </c>
       <c r="DC12">
-        <v>90.3</v>
+        <v>43.6</v>
       </c>
       <c r="DD12" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="DE12" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="DF12">
-        <v>95.3</v>
+        <v>42.7</v>
       </c>
       <c r="DG12">
-        <v>95.3</v>
+        <v>42.7</v>
       </c>
       <c r="DH12">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="DI12">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="DJ12">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="DK12">
         <v>-0</v>
@@ -8830,7 +8877,7 @@
         <v>-0</v>
       </c>
       <c r="DN12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12">
         <v>-0</v>
@@ -8938,25 +8985,25 @@
         <v>0</v>
       </c>
       <c r="EX12" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="EY12">
-        <v>13</v>
+        <v>15.9</v>
       </c>
       <c r="EZ12" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="FA12">
         <v>79</v>
       </c>
       <c r="FB12">
-        <v>78.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="FC12">
         <v>5</v>
       </c>
       <c r="FD12">
-        <v>6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="13" spans="1:160">
@@ -8973,40 +9020,40 @@
         <v>120</v>
       </c>
       <c r="E13" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F13" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G13" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H13" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I13" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J13">
-        <v>405.9</v>
+        <v>74.5</v>
       </c>
       <c r="K13">
-        <v>22.5</v>
+        <v>5.3</v>
       </c>
       <c r="L13">
         <v>5</v>
       </c>
       <c r="M13">
-        <v>1.84</v>
+        <v>0.89</v>
       </c>
       <c r="N13">
-        <v>2.78</v>
+        <v>1.7</v>
       </c>
       <c r="O13">
-        <v>13.52</v>
+        <v>16.16</v>
       </c>
       <c r="P13">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -9042,7 +9089,7 @@
         <v>100</v>
       </c>
       <c r="AE13" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AF13">
         <v>0</v>
@@ -9057,28 +9104,28 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AK13" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL13" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AM13" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AN13">
         <v>0.5</v>
       </c>
       <c r="AO13">
-        <v>20.4</v>
+        <v>14.3</v>
       </c>
       <c r="AP13">
-        <v>84.3</v>
+        <v>86.3</v>
       </c>
       <c r="AQ13">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -9087,7 +9134,7 @@
         <v>0.35</v>
       </c>
       <c r="AT13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU13">
         <v>0</v>
@@ -9102,49 +9149,49 @@
         <v>0</v>
       </c>
       <c r="AY13">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="AZ13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA13" t="s">
         <v>130</v>
       </c>
       <c r="BB13">
-        <v>78.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="BC13">
-        <v>85.2</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="BD13">
-        <v>75.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="BE13">
-        <v>90.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="BF13">
-        <v>1015.9</v>
+        <v>1015.8</v>
       </c>
       <c r="BG13">
         <v>1017</v>
       </c>
       <c r="BH13">
-        <v>97.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="BI13">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="BJ13">
-        <v>0.021</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="BK13">
-        <v>24.7</v>
+        <v>29.4</v>
       </c>
       <c r="BL13">
-        <v>944</v>
+        <v>1561</v>
       </c>
       <c r="BM13">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BN13">
         <v>0</v>
@@ -9153,10 +9200,10 @@
         <v>0</v>
       </c>
       <c r="BP13" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BQ13" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BR13">
         <v>0.187</v>
@@ -9177,7 +9224,7 @@
         <v>0</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY13">
         <v>-0</v>
@@ -9186,7 +9233,7 @@
         <v>-0</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13">
         <v>-0</v>
@@ -9195,7 +9242,7 @@
         <v>-0</v>
       </c>
       <c r="CD13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13">
         <v>-0</v>
@@ -9204,7 +9251,7 @@
         <v>-0</v>
       </c>
       <c r="CG13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH13">
         <v>-0</v>
@@ -9213,7 +9260,7 @@
         <v>-0</v>
       </c>
       <c r="CJ13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK13">
         <v>-0</v>
@@ -9222,19 +9269,19 @@
         <v>-0</v>
       </c>
       <c r="CM13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CR13">
         <v>0</v>
@@ -9255,7 +9302,7 @@
         <v>0</v>
       </c>
       <c r="CX13">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="CY13">
         <v>0</v>
@@ -9267,10 +9314,10 @@
         <v>0</v>
       </c>
       <c r="DB13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="DC13">
-        <v>104.1</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="DD13" t="s">
         <v>361</v>
@@ -9279,25 +9326,25 @@
         <v>361</v>
       </c>
       <c r="DF13">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="DG13">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="DH13">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="DI13">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="DJ13">
-        <v>1.8</v>
+        <v>10.1</v>
       </c>
       <c r="DK13">
         <v>-0</v>
       </c>
       <c r="DL13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13">
         <v>-0</v>
@@ -9309,7 +9356,7 @@
         <v>-0</v>
       </c>
       <c r="DP13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13">
         <v>-0</v>
@@ -9318,7 +9365,7 @@
         <v>-0</v>
       </c>
       <c r="DS13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT13">
         <v>-0</v>
@@ -9411,25 +9458,25 @@
         <v>0</v>
       </c>
       <c r="EX13" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="EY13">
-        <v>11.9</v>
+        <v>13.2</v>
       </c>
       <c r="EZ13" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="FA13">
         <v>79</v>
       </c>
       <c r="FB13">
-        <v>78</v>
+        <v>79.5</v>
       </c>
       <c r="FC13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="FD13">
-        <v>6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="14" spans="1:160">
@@ -9446,43 +9493,43 @@
         <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F14" t="s">
         <v>117</v>
       </c>
       <c r="G14" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H14" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I14" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J14">
-        <v>66.09999999999999</v>
+        <v>35.3</v>
       </c>
       <c r="K14">
-        <v>21.5</v>
+        <v>4.3</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
       <c r="M14">
-        <v>0.79</v>
+        <v>0.48</v>
       </c>
       <c r="N14">
-        <v>1.11</v>
+        <v>0.88</v>
       </c>
       <c r="O14">
-        <v>2</v>
+        <v>0.61</v>
       </c>
       <c r="P14">
-        <v>9.4</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -9515,7 +9562,7 @@
         <v>100</v>
       </c>
       <c r="AE14" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AF14">
         <v>0</v>
@@ -9530,25 +9577,25 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AK14" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL14" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AM14" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AN14">
         <v>0.5</v>
       </c>
       <c r="AO14">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="AP14">
-        <v>94.7</v>
+        <v>96.5</v>
       </c>
       <c r="AQ14">
         <v>53.7</v>
@@ -9557,7 +9604,7 @@
         <v>0.82</v>
       </c>
       <c r="AS14">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="AT14">
         <v>8</v>
@@ -9575,49 +9622,49 @@
         <v>0.5</v>
       </c>
       <c r="AY14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="BB14">
         <v>56.5</v>
       </c>
       <c r="BC14">
-        <v>54.4</v>
+        <v>53.9</v>
       </c>
       <c r="BD14">
-        <v>50.7</v>
+        <v>51.3</v>
       </c>
       <c r="BE14">
-        <v>80.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="BF14">
-        <v>996.8</v>
+        <v>996</v>
       </c>
       <c r="BG14">
-        <v>1022.3</v>
+        <v>1021.5</v>
       </c>
       <c r="BH14">
-        <v>41.5</v>
+        <v>20.5</v>
       </c>
       <c r="BI14">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="BJ14">
         <v>0</v>
       </c>
       <c r="BK14">
-        <v>30.5</v>
+        <v>33.7</v>
       </c>
       <c r="BL14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM14">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BN14">
         <v>0</v>
@@ -9626,10 +9673,10 @@
         <v>0</v>
       </c>
       <c r="BP14" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BQ14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BR14">
         <v>0.145</v>
@@ -9728,7 +9775,7 @@
         <v>0</v>
       </c>
       <c r="CX14">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="CY14">
         <v>0</v>
@@ -9740,28 +9787,28 @@
         <v>0</v>
       </c>
       <c r="DB14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="DC14">
-        <v>172</v>
+        <v>172.4</v>
       </c>
       <c r="DD14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="DE14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="DF14">
-        <v>91.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="DG14">
-        <v>91.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="DH14">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="DI14">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="DJ14">
         <v>0.6</v>
@@ -9884,13 +9931,13 @@
         <v>0</v>
       </c>
       <c r="EX14" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="EY14">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="EZ14" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="FA14">
         <v>57</v>
@@ -9902,7 +9949,7 @@
         <v>5</v>
       </c>
       <c r="FD14">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="15" spans="1:160">
@@ -9919,43 +9966,43 @@
         <v>121</v>
       </c>
       <c r="E15" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F15" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G15" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H15" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I15" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J15">
-        <v>66.09999999999999</v>
+        <v>35.3</v>
       </c>
       <c r="K15">
-        <v>22.5</v>
+        <v>5.3</v>
       </c>
       <c r="L15">
         <v>5</v>
       </c>
       <c r="M15">
-        <v>0.35</v>
+        <v>0.74</v>
       </c>
       <c r="N15">
-        <v>1.57</v>
+        <v>0.75</v>
       </c>
       <c r="O15">
-        <v>2.25</v>
+        <v>1.39</v>
       </c>
       <c r="P15">
-        <v>9.1</v>
+        <v>4.9</v>
       </c>
       <c r="Q15">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -9988,7 +10035,7 @@
         <v>100</v>
       </c>
       <c r="AE15" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AF15">
         <v>0</v>
@@ -10003,34 +10050,34 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AK15" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL15" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AM15" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AN15">
         <v>0.5</v>
       </c>
       <c r="AO15">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="AP15">
-        <v>94.3</v>
+        <v>96</v>
       </c>
       <c r="AQ15">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="AR15">
         <v>0.82</v>
       </c>
       <c r="AS15">
-        <v>0.779</v>
+        <v>0.784</v>
       </c>
       <c r="AT15">
         <v>8</v>
@@ -10048,49 +10095,49 @@
         <v>0.5</v>
       </c>
       <c r="AY15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA15" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="BB15">
-        <v>55.5</v>
+        <v>55.7</v>
       </c>
       <c r="BC15">
-        <v>54.9</v>
+        <v>52.6</v>
       </c>
       <c r="BD15">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="BE15">
-        <v>85.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="BF15">
-        <v>996.6</v>
+        <v>995.7</v>
       </c>
       <c r="BG15">
-        <v>1022.1</v>
+        <v>1021.2</v>
       </c>
       <c r="BH15">
-        <v>66</v>
+        <v>24.6</v>
       </c>
       <c r="BI15">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="BJ15">
         <v>0</v>
       </c>
       <c r="BK15">
-        <v>29.8</v>
+        <v>32.2</v>
       </c>
       <c r="BL15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM15">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BN15">
         <v>0</v>
@@ -10099,13 +10146,13 @@
         <v>0</v>
       </c>
       <c r="BP15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BQ15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BR15">
-        <v>0.144</v>
+        <v>0.143</v>
       </c>
       <c r="BS15">
         <v>0</v>
@@ -10201,7 +10248,7 @@
         <v>0</v>
       </c>
       <c r="CX15">
-        <v>13.4</v>
+        <v>15.5</v>
       </c>
       <c r="CY15">
         <v>0</v>
@@ -10213,31 +10260,31 @@
         <v>0</v>
       </c>
       <c r="DB15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="DC15">
-        <v>176.5</v>
+        <v>178.9</v>
       </c>
       <c r="DD15" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="DE15" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="DF15">
-        <v>91.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="DG15">
-        <v>91.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="DH15">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="DI15">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="DJ15">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="DK15">
         <v>-0</v>
@@ -10357,25 +10404,25 @@
         <v>0</v>
       </c>
       <c r="EX15" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="EY15">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="EZ15" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="FA15">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="FB15">
-        <v>55.9</v>
+        <v>55.5</v>
       </c>
       <c r="FC15">
         <v>5</v>
       </c>
       <c r="FD15">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="16" spans="1:160">
@@ -10392,43 +10439,43 @@
         <v>121</v>
       </c>
       <c r="E16" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F16" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G16" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H16" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I16" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J16">
-        <v>66.09999999999999</v>
+        <v>35.3</v>
       </c>
       <c r="K16">
-        <v>23.5</v>
+        <v>6.3</v>
       </c>
       <c r="L16">
         <v>5</v>
       </c>
       <c r="M16">
-        <v>0.35</v>
+        <v>0.58</v>
       </c>
       <c r="N16">
-        <v>1.57</v>
+        <v>0.83</v>
       </c>
       <c r="O16">
-        <v>2.75</v>
+        <v>3.01</v>
       </c>
       <c r="P16">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q16">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -10461,7 +10508,7 @@
         <v>100</v>
       </c>
       <c r="AE16" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AF16">
         <v>0</v>
@@ -10476,34 +10523,34 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AK16" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL16" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AM16" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AN16">
         <v>0.5</v>
       </c>
       <c r="AO16">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="AP16">
-        <v>93.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AQ16">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="AR16">
         <v>0.82</v>
       </c>
       <c r="AS16">
-        <v>0.788</v>
+        <v>0.794</v>
       </c>
       <c r="AT16">
         <v>8</v>
@@ -10521,49 +10568,49 @@
         <v>0.5</v>
       </c>
       <c r="AY16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BB16">
-        <v>54.9</v>
+        <v>55.7</v>
       </c>
       <c r="BC16">
-        <v>54.2</v>
+        <v>52.5</v>
       </c>
       <c r="BD16">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="BE16">
-        <v>87.8</v>
+        <v>85.8</v>
       </c>
       <c r="BF16">
-        <v>996.1</v>
+        <v>995.4</v>
       </c>
       <c r="BG16">
-        <v>1021.5</v>
+        <v>1020.8</v>
       </c>
       <c r="BH16">
-        <v>64.90000000000001</v>
+        <v>56.5</v>
       </c>
       <c r="BI16">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="BJ16">
         <v>0</v>
       </c>
       <c r="BK16">
-        <v>29.7</v>
+        <v>32.1</v>
       </c>
       <c r="BL16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BM16">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BN16">
         <v>0</v>
@@ -10572,10 +10619,10 @@
         <v>0</v>
       </c>
       <c r="BP16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BQ16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BR16">
         <v>0.142</v>
@@ -10596,7 +10643,7 @@
         <v>0</v>
       </c>
       <c r="BX16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY16">
         <v>-0</v>
@@ -10605,7 +10652,7 @@
         <v>-0</v>
       </c>
       <c r="CA16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB16">
         <v>-0</v>
@@ -10614,7 +10661,7 @@
         <v>-0</v>
       </c>
       <c r="CD16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE16">
         <v>-0</v>
@@ -10623,7 +10670,7 @@
         <v>-0</v>
       </c>
       <c r="CG16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH16">
         <v>-0</v>
@@ -10632,7 +10679,7 @@
         <v>-0</v>
       </c>
       <c r="CJ16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16">
         <v>-0</v>
@@ -10641,19 +10688,19 @@
         <v>-0</v>
       </c>
       <c r="CM16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CR16">
         <v>0</v>
@@ -10674,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="CX16">
-        <v>13.3</v>
+        <v>14.9</v>
       </c>
       <c r="CY16">
         <v>0</v>
@@ -10686,37 +10733,37 @@
         <v>0</v>
       </c>
       <c r="DB16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="DC16">
-        <v>181.3</v>
+        <v>184.2</v>
       </c>
       <c r="DD16" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="DE16" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="DF16">
-        <v>94.09999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="DG16">
-        <v>94.09999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="DH16">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="DI16">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="DJ16">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DK16">
         <v>-0</v>
       </c>
       <c r="DL16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM16">
         <v>-0</v>
@@ -10728,7 +10775,7 @@
         <v>-0</v>
       </c>
       <c r="DP16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ16">
         <v>-0</v>
@@ -10737,7 +10784,7 @@
         <v>-0</v>
       </c>
       <c r="DS16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT16">
         <v>-0</v>
@@ -10830,16 +10877,16 @@
         <v>0</v>
       </c>
       <c r="EX16" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="EY16">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="EZ16" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="FA16">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="FB16">
         <v>55.5</v>
@@ -10848,7 +10895,7 @@
         <v>5</v>
       </c>
       <c r="FD16">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="17" spans="1:160">
@@ -10865,43 +10912,43 @@
         <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F17" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G17" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H17" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I17" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J17">
-        <v>66.09999999999999</v>
+        <v>35.3</v>
       </c>
       <c r="K17">
-        <v>24.5</v>
+        <v>7.3</v>
       </c>
       <c r="L17">
         <v>5</v>
       </c>
       <c r="M17">
-        <v>0.43</v>
+        <v>0.27</v>
       </c>
       <c r="N17">
-        <v>1.54</v>
+        <v>0.83</v>
       </c>
       <c r="O17">
-        <v>3.66</v>
+        <v>7.42</v>
       </c>
       <c r="P17">
-        <v>20.9</v>
+        <v>11.3</v>
       </c>
       <c r="Q17">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -10934,7 +10981,7 @@
         <v>100</v>
       </c>
       <c r="AE17" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AF17">
         <v>0</v>
@@ -10949,28 +10996,28 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AK17" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL17" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AM17" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AN17">
         <v>0.5</v>
       </c>
       <c r="AO17">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="AP17">
-        <v>92.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AQ17">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="AR17">
         <v>0.82</v>
@@ -10997,46 +11044,46 @@
         <v>3</v>
       </c>
       <c r="AZ17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BA17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BB17">
-        <v>54.4</v>
+        <v>55.2</v>
       </c>
       <c r="BC17">
-        <v>53.8</v>
+        <v>53.4</v>
       </c>
       <c r="BD17">
-        <v>51.1</v>
+        <v>51.3</v>
       </c>
       <c r="BE17">
-        <v>88.7</v>
+        <v>86.2</v>
       </c>
       <c r="BF17">
-        <v>995.7</v>
+        <v>995.3</v>
       </c>
       <c r="BG17">
-        <v>1021.1</v>
+        <v>1020.8</v>
       </c>
       <c r="BH17">
-        <v>72.8</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="BI17">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BJ17">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="BK17">
-        <v>30.3</v>
+        <v>32.6</v>
       </c>
       <c r="BL17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BM17">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN17">
         <v>0</v>
@@ -11045,10 +11092,10 @@
         <v>0</v>
       </c>
       <c r="BP17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BQ17" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BR17">
         <v>0.138</v>
@@ -11147,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="CX17">
-        <v>13.4</v>
+        <v>12.7</v>
       </c>
       <c r="CY17">
         <v>0</v>
@@ -11159,31 +11206,31 @@
         <v>0</v>
       </c>
       <c r="DB17" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="DC17">
         <v>199</v>
       </c>
       <c r="DD17" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="DE17" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="DF17">
-        <v>85.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="DG17">
-        <v>85.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="DH17">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="DI17">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="DJ17">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="DK17">
         <v>-0</v>
@@ -11303,16 +11350,16 @@
         <v>0</v>
       </c>
       <c r="EX17" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="EY17">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="EZ17" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="FA17">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="FB17">
         <v>55.4</v>
@@ -11321,7 +11368,7 @@
         <v>5</v>
       </c>
       <c r="FD17">
-        <v>4.9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11423,40 +11470,40 @@
         <v>119</v>
       </c>
       <c r="E2">
-        <v>64.90000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="F2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G2">
-        <v>86.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2">
         <v>7</v>
       </c>
       <c r="J2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
       <c r="L2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M2">
-        <v>102.2</v>
+        <v>103</v>
       </c>
       <c r="N2">
-        <v>3585</v>
+        <v>3672</v>
       </c>
       <c r="O2" t="s">
         <v>122</v>
       </c>
       <c r="P2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="Q2">
         <v>5</v>
@@ -11479,10 +11526,10 @@
         <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G3">
-        <v>85.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -11497,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M3">
-        <v>80.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="N3">
         <v>858</v>
@@ -11509,7 +11556,7 @@
         <v>123</v>
       </c>
       <c r="P3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -11532,10 +11579,10 @@
         <v>49.9</v>
       </c>
       <c r="F4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G4">
-        <v>94.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -11550,10 +11597,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M4">
-        <v>55.6</v>
+        <v>55.9</v>
       </c>
       <c r="N4">
         <v>858</v>
@@ -11562,7 +11609,7 @@
         <v>124</v>
       </c>
       <c r="P4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="Q4">
         <v>5</v>
@@ -11582,13 +11629,13 @@
         <v>118</v>
       </c>
       <c r="E5">
-        <v>46.6</v>
+        <v>46.3</v>
       </c>
       <c r="F5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G5">
-        <v>92.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H5">
         <v>-2</v>
@@ -11597,25 +11644,25 @@
         <v>-2</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="K5">
         <v>-4</v>
       </c>
       <c r="L5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M5">
-        <v>64.5</v>
+        <v>65</v>
       </c>
       <c r="N5">
-        <v>560</v>
+        <v>594</v>
       </c>
       <c r="O5" t="s">
         <v>122</v>
       </c>
       <c r="P5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="Q5">
         <v>5</v>
